--- a/research/traditional_assets/database/data/israel/israel_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_farming_agriculture.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08385587254441154</v>
+        <v>0.0836976540375594</v>
       </c>
       <c r="C2">
-        <v>48.09360155326834</v>
+        <v>47.69723277353712</v>
       </c>
       <c r="D2">
-        <v>44.34360155326834</v>
+        <v>44.42813277353712</v>
       </c>
       <c r="E2">
-        <v>-1.49</v>
+        <v>-1.0091</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.4809</v>
       </c>
       <c r="G2">
         <v>3.75</v>
@@ -1579,28 +1579,28 @@
         <v>5.37</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02418927</v>
       </c>
       <c r="N2">
-        <v>5.37</v>
+        <v>5.34581073</v>
       </c>
       <c r="O2">
-        <v>1.2351</v>
+        <v>1.2295364679</v>
       </c>
       <c r="P2">
-        <v>4.1349</v>
+        <v>4.1162742621</v>
       </c>
       <c r="Q2">
-        <v>4.6949</v>
+        <v>4.6762742621</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08385587254441154</v>
+        <v>0.08415186266420141</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5932911180612612</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>221.9992583488464</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0836976540375594</v>
+        <v>0.08353943553070725</v>
       </c>
       <c r="C3">
-        <v>47.69723277353712</v>
+        <v>47.30118688930038</v>
       </c>
       <c r="D3">
-        <v>44.42813277353712</v>
+        <v>44.51298688930038</v>
       </c>
       <c r="E3">
-        <v>-1.0091</v>
+        <v>-0.5281999999999999</v>
       </c>
       <c r="F3">
-        <v>0.4809</v>
+        <v>0.9618000000000001</v>
       </c>
       <c r="G3">
         <v>3.75</v>
@@ -1661,28 +1661,28 @@
         <v>5.37</v>
       </c>
       <c r="M3">
-        <v>0.02418927</v>
+        <v>0.04837854</v>
       </c>
       <c r="N3">
-        <v>5.34581073</v>
+        <v>5.32162146</v>
       </c>
       <c r="O3">
-        <v>1.2295364679</v>
+        <v>1.2239729358</v>
       </c>
       <c r="P3">
-        <v>4.1162742621</v>
+        <v>4.0976485242</v>
       </c>
       <c r="Q3">
-        <v>4.6762742621</v>
+        <v>4.6576485242</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08415186266420141</v>
+        <v>0.08445389339868087</v>
       </c>
       <c r="T3">
-        <v>0.5932911180612612</v>
+        <v>0.5979634374663744</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>221.9992583488464</v>
+        <v>110.9996291744232</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08353943553070725</v>
+        <v>0.08338121702385511</v>
       </c>
       <c r="C4">
-        <v>47.30118688930038</v>
+        <v>46.90546575421074</v>
       </c>
       <c r="D4">
-        <v>44.51298688930038</v>
+        <v>44.59816575421075</v>
       </c>
       <c r="E4">
-        <v>-0.5281999999999999</v>
+        <v>-0.0472999999999999</v>
       </c>
       <c r="F4">
-        <v>0.9618000000000001</v>
+        <v>1.4427</v>
       </c>
       <c r="G4">
         <v>3.75</v>
@@ -1743,28 +1743,28 @@
         <v>5.37</v>
       </c>
       <c r="M4">
-        <v>0.04837854</v>
+        <v>0.07256781</v>
       </c>
       <c r="N4">
-        <v>5.32162146</v>
+        <v>5.29743219</v>
       </c>
       <c r="O4">
-        <v>1.2239729358</v>
+        <v>1.2184094037</v>
       </c>
       <c r="P4">
-        <v>4.0976485242</v>
+        <v>4.0790227863</v>
       </c>
       <c r="Q4">
-        <v>4.6576485242</v>
+        <v>4.6390227863</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08445389339868087</v>
+        <v>0.08476215157098464</v>
       </c>
       <c r="T4">
-        <v>0.5979634374663744</v>
+        <v>0.6027320933540671</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>110.9996291744232</v>
+        <v>73.99975278294882</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08338121702385511</v>
+        <v>0.08322299851700295</v>
       </c>
       <c r="C5">
-        <v>46.90546575421074</v>
+        <v>46.51007123613645</v>
       </c>
       <c r="D5">
-        <v>44.59816575421075</v>
+        <v>44.68367123613645</v>
       </c>
       <c r="E5">
-        <v>-0.0472999999999999</v>
+        <v>0.4336000000000002</v>
       </c>
       <c r="F5">
-        <v>1.4427</v>
+        <v>1.9236</v>
       </c>
       <c r="G5">
         <v>3.75</v>
@@ -1825,28 +1825,28 @@
         <v>5.37</v>
       </c>
       <c r="M5">
-        <v>0.07256781</v>
+        <v>0.09675708000000001</v>
       </c>
       <c r="N5">
-        <v>5.29743219</v>
+        <v>5.27324292</v>
       </c>
       <c r="O5">
-        <v>1.2184094037</v>
+        <v>1.2128458716</v>
       </c>
       <c r="P5">
-        <v>4.0790227863</v>
+        <v>4.0603970484</v>
       </c>
       <c r="Q5">
-        <v>4.6390227863</v>
+        <v>4.6203970484</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08476215157098464</v>
+        <v>0.08507683178854475</v>
       </c>
       <c r="T5">
-        <v>0.6027320933540671</v>
+        <v>0.60760009623942</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>73.99975278294882</v>
+        <v>55.4998145872116</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08322299851700295</v>
+        <v>0.0830647800101508</v>
       </c>
       <c r="C6">
-        <v>46.51007123613645</v>
+        <v>46.11500521729787</v>
       </c>
       <c r="D6">
-        <v>44.68367123613645</v>
+        <v>44.76950521729787</v>
       </c>
       <c r="E6">
-        <v>0.4336000000000002</v>
+        <v>0.9145000000000005</v>
       </c>
       <c r="F6">
-        <v>1.9236</v>
+        <v>2.404500000000001</v>
       </c>
       <c r="G6">
         <v>3.75</v>
@@ -1907,28 +1907,28 @@
         <v>5.37</v>
       </c>
       <c r="M6">
-        <v>0.09675708000000001</v>
+        <v>0.12094635</v>
       </c>
       <c r="N6">
-        <v>5.27324292</v>
+        <v>5.24905365</v>
       </c>
       <c r="O6">
-        <v>1.2128458716</v>
+        <v>1.2072823395</v>
       </c>
       <c r="P6">
-        <v>4.0603970484</v>
+        <v>4.041771310500001</v>
       </c>
       <c r="Q6">
-        <v>4.6203970484</v>
+        <v>4.6017713105</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08507683178854475</v>
+        <v>0.08539813685279032</v>
       </c>
       <c r="T6">
-        <v>0.60760009623942</v>
+        <v>0.6125705833960436</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>55.4998145872116</v>
+        <v>44.39985166976928</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0830647800101508</v>
+        <v>0.08290656150329866</v>
       </c>
       <c r="C7">
-        <v>46.11500521729787</v>
+        <v>45.72026959440559</v>
       </c>
       <c r="D7">
-        <v>44.76950521729787</v>
+        <v>44.8556695944056</v>
       </c>
       <c r="E7">
-        <v>0.9145000000000005</v>
+        <v>1.395400000000001</v>
       </c>
       <c r="F7">
-        <v>2.404500000000001</v>
+        <v>2.885400000000001</v>
       </c>
       <c r="G7">
         <v>3.75</v>
@@ -1989,28 +1989,28 @@
         <v>5.37</v>
       </c>
       <c r="M7">
-        <v>0.12094635</v>
+        <v>0.14513562</v>
       </c>
       <c r="N7">
-        <v>5.24905365</v>
+        <v>5.22486438</v>
       </c>
       <c r="O7">
-        <v>1.2072823395</v>
+        <v>1.2017188074</v>
       </c>
       <c r="P7">
-        <v>4.041771310500001</v>
+        <v>4.0231455726</v>
       </c>
       <c r="Q7">
-        <v>4.6017713105</v>
+        <v>4.583145572599999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08539813685279032</v>
+        <v>0.08572627819499858</v>
       </c>
       <c r="T7">
-        <v>0.6125705833960436</v>
+        <v>0.6176468255985529</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.39985166976928</v>
+        <v>36.99987639147439</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08290656150329864</v>
+        <v>0.08274834299644651</v>
       </c>
       <c r="C8">
-        <v>45.72026959440561</v>
+        <v>45.32586627880024</v>
       </c>
       <c r="D8">
-        <v>44.8556695944056</v>
+        <v>44.94216627880024</v>
       </c>
       <c r="E8">
-        <v>1.3954</v>
+        <v>1.8763</v>
       </c>
       <c r="F8">
-        <v>2.8854</v>
+        <v>3.3663</v>
       </c>
       <c r="G8">
         <v>3.75</v>
@@ -2071,28 +2071,28 @@
         <v>5.37</v>
       </c>
       <c r="M8">
-        <v>0.14513562</v>
+        <v>0.16932489</v>
       </c>
       <c r="N8">
-        <v>5.224864380000001</v>
+        <v>5.20067511</v>
       </c>
       <c r="O8">
-        <v>1.2017188074</v>
+        <v>1.1961552753</v>
       </c>
       <c r="P8">
-        <v>4.023145572600001</v>
+        <v>4.0045198347</v>
       </c>
       <c r="Q8">
-        <v>4.5831455726</v>
+        <v>4.5645198347</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08572627819499856</v>
+        <v>0.08606147634026506</v>
       </c>
       <c r="T8">
-        <v>0.6176468255985528</v>
+        <v>0.6228322343000408</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.99987639147441</v>
+        <v>31.71417976412092</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0827483429964465</v>
+        <v>0.08259012448959437</v>
       </c>
       <c r="C9">
-        <v>45.32586627880025</v>
+        <v>44.93179719659368</v>
       </c>
       <c r="D9">
-        <v>44.94216627880025</v>
+        <v>45.02899719659368</v>
       </c>
       <c r="E9">
-        <v>1.876300000000001</v>
+        <v>2.357200000000001</v>
       </c>
       <c r="F9">
-        <v>3.366300000000001</v>
+        <v>3.8472</v>
       </c>
       <c r="G9">
         <v>3.75</v>
@@ -2153,28 +2153,28 @@
         <v>5.37</v>
       </c>
       <c r="M9">
-        <v>0.16932489</v>
+        <v>0.19351416</v>
       </c>
       <c r="N9">
-        <v>5.20067511</v>
+        <v>5.17648584</v>
       </c>
       <c r="O9">
-        <v>1.1961552753</v>
+        <v>1.1905917432</v>
       </c>
       <c r="P9">
-        <v>4.0045198347</v>
+        <v>3.9858940968</v>
       </c>
       <c r="Q9">
-        <v>4.5645198347</v>
+        <v>4.5458940968</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08606147634026506</v>
+        <v>0.08640396140173301</v>
       </c>
       <c r="T9">
-        <v>0.6228322343000408</v>
+        <v>0.628130369277648</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.71417976412091</v>
+        <v>27.7499072936058</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08259012448959437</v>
+        <v>0.08243190598274223</v>
       </c>
       <c r="C10">
-        <v>44.93179719659368</v>
+        <v>44.53806428881203</v>
       </c>
       <c r="D10">
-        <v>45.02899719659368</v>
+        <v>45.11616428881203</v>
       </c>
       <c r="E10">
-        <v>2.357200000000001</v>
+        <v>2.8381</v>
       </c>
       <c r="F10">
-        <v>3.8472</v>
+        <v>4.3281</v>
       </c>
       <c r="G10">
         <v>3.75</v>
@@ -2235,28 +2235,28 @@
         <v>5.37</v>
       </c>
       <c r="M10">
-        <v>0.19351416</v>
+        <v>0.21770343</v>
       </c>
       <c r="N10">
-        <v>5.17648584</v>
+        <v>5.15229657</v>
       </c>
       <c r="O10">
-        <v>1.1905917432</v>
+        <v>1.1850282111</v>
       </c>
       <c r="P10">
-        <v>3.9858940968</v>
+        <v>3.9672683589</v>
       </c>
       <c r="Q10">
-        <v>4.5458940968</v>
+        <v>4.527268358899999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08640396140173301</v>
+        <v>0.08675397360740904</v>
       </c>
       <c r="T10">
-        <v>0.628130369277648</v>
+        <v>0.6335449467822356</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.7499072936058</v>
+        <v>24.66658426098293</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08243190598274223</v>
+        <v>0.08227368747589008</v>
       </c>
       <c r="C11">
-        <v>44.53806428881203</v>
+        <v>44.14466951154036</v>
       </c>
       <c r="D11">
-        <v>45.11616428881203</v>
+        <v>45.20366951154035</v>
       </c>
       <c r="E11">
-        <v>2.8381</v>
+        <v>3.319</v>
       </c>
       <c r="F11">
-        <v>4.3281</v>
+        <v>4.809</v>
       </c>
       <c r="G11">
         <v>3.75</v>
@@ -2317,28 +2317,28 @@
         <v>5.37</v>
       </c>
       <c r="M11">
-        <v>0.21770343</v>
+        <v>0.2418927</v>
       </c>
       <c r="N11">
-        <v>5.15229657</v>
+        <v>5.1281073</v>
       </c>
       <c r="O11">
-        <v>1.1850282111</v>
+        <v>1.179464679</v>
       </c>
       <c r="P11">
-        <v>3.9672683589</v>
+        <v>3.948642621</v>
       </c>
       <c r="Q11">
-        <v>4.527268358899999</v>
+        <v>4.508642621</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08675397360740904</v>
+        <v>0.08711176386210008</v>
       </c>
       <c r="T11">
-        <v>0.6335449467822356</v>
+        <v>0.6390798482313695</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.66658426098293</v>
+        <v>22.19992583488464</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08227368747589008</v>
+        <v>0.08211546896903794</v>
       </c>
       <c r="C12">
-        <v>44.14466951154036</v>
+        <v>43.75161483606887</v>
       </c>
       <c r="D12">
-        <v>45.20366951154035</v>
+        <v>45.29151483606887</v>
       </c>
       <c r="E12">
-        <v>3.319000000000001</v>
+        <v>3.7999</v>
       </c>
       <c r="F12">
-        <v>4.809000000000001</v>
+        <v>5.2899</v>
       </c>
       <c r="G12">
         <v>3.75</v>
@@ -2399,28 +2399,28 @@
         <v>5.37</v>
       </c>
       <c r="M12">
-        <v>0.2418927</v>
+        <v>0.26608197</v>
       </c>
       <c r="N12">
-        <v>5.1281073</v>
+        <v>5.10391803</v>
       </c>
       <c r="O12">
-        <v>1.179464679</v>
+        <v>1.1739011469</v>
       </c>
       <c r="P12">
-        <v>3.948642621</v>
+        <v>3.9300168831</v>
       </c>
       <c r="Q12">
-        <v>4.508642621</v>
+        <v>4.490016883099999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08711176386210008</v>
+        <v>0.08747759434723364</v>
       </c>
       <c r="T12">
-        <v>0.6390798482313695</v>
+        <v>0.6447391294883493</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.19992583488464</v>
+        <v>20.18175075898604</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08211546896903794</v>
+        <v>0.08195725046218577</v>
       </c>
       <c r="C13">
-        <v>43.75161483606887</v>
+        <v>43.35890224904112</v>
       </c>
       <c r="D13">
-        <v>45.29151483606887</v>
+        <v>45.37970224904112</v>
       </c>
       <c r="E13">
-        <v>3.7999</v>
+        <v>4.2808</v>
       </c>
       <c r="F13">
-        <v>5.2899</v>
+        <v>5.7708</v>
       </c>
       <c r="G13">
         <v>3.75</v>
@@ -2481,28 +2481,28 @@
         <v>5.37</v>
       </c>
       <c r="M13">
-        <v>0.26608197</v>
+        <v>0.29027124</v>
       </c>
       <c r="N13">
-        <v>5.10391803</v>
+        <v>5.07972876</v>
       </c>
       <c r="O13">
-        <v>1.1739011469</v>
+        <v>1.1683376148</v>
       </c>
       <c r="P13">
-        <v>3.9300168831</v>
+        <v>3.9113911452</v>
       </c>
       <c r="Q13">
-        <v>4.490016883099999</v>
+        <v>4.4713911452</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08747759434723364</v>
+        <v>0.08785173916157475</v>
       </c>
       <c r="T13">
-        <v>0.6447391294883493</v>
+        <v>0.6505270307738966</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.18175075898604</v>
+        <v>18.4999381957372</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08195725046218577</v>
+        <v>0.08179903195533363</v>
       </c>
       <c r="C14">
-        <v>43.35890224904112</v>
+        <v>42.9665337526036</v>
       </c>
       <c r="D14">
-        <v>45.37970224904112</v>
+        <v>45.4682337526036</v>
       </c>
       <c r="E14">
-        <v>4.2808</v>
+        <v>4.7617</v>
       </c>
       <c r="F14">
-        <v>5.7708</v>
+        <v>6.2517</v>
       </c>
       <c r="G14">
         <v>3.75</v>
@@ -2563,28 +2563,28 @@
         <v>5.37</v>
       </c>
       <c r="M14">
-        <v>0.29027124</v>
+        <v>0.31446051</v>
       </c>
       <c r="N14">
-        <v>5.07972876</v>
+        <v>5.05553949</v>
       </c>
       <c r="O14">
-        <v>1.1683376148</v>
+        <v>1.1627740827</v>
       </c>
       <c r="P14">
-        <v>3.9113911452</v>
+        <v>3.8927654073</v>
       </c>
       <c r="Q14">
-        <v>4.4713911452</v>
+        <v>4.452765407299999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08785173916157475</v>
+        <v>0.08823448500613061</v>
       </c>
       <c r="T14">
-        <v>0.6505270307738966</v>
+        <v>0.6564479872614106</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.4999381957372</v>
+        <v>17.07686602683434</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08179903195533363</v>
+        <v>0.08164081344848148</v>
       </c>
       <c r="C15">
-        <v>42.9665337526036</v>
+        <v>42.57451136455735</v>
       </c>
       <c r="D15">
-        <v>45.4682337526036</v>
+        <v>45.55711136455735</v>
       </c>
       <c r="E15">
-        <v>4.7617</v>
+        <v>5.242600000000001</v>
       </c>
       <c r="F15">
-        <v>6.2517</v>
+        <v>6.732600000000001</v>
       </c>
       <c r="G15">
         <v>3.75</v>
@@ -2645,28 +2645,28 @@
         <v>5.37</v>
       </c>
       <c r="M15">
-        <v>0.31446051</v>
+        <v>0.3386497800000001</v>
       </c>
       <c r="N15">
-        <v>5.05553949</v>
+        <v>5.03135022</v>
       </c>
       <c r="O15">
-        <v>1.1627740827</v>
+        <v>1.1572105506</v>
       </c>
       <c r="P15">
-        <v>3.8927654073</v>
+        <v>3.8741396694</v>
       </c>
       <c r="Q15">
-        <v>4.452765407299999</v>
+        <v>4.434139669399999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08823448500613061</v>
+        <v>0.08862613191683893</v>
       </c>
       <c r="T15">
-        <v>0.6564479872614106</v>
+        <v>0.662506640411425</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.07686602683434</v>
+        <v>15.85708988206046</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08164081344848148</v>
+        <v>0.08148259494162935</v>
       </c>
       <c r="C16">
-        <v>42.57451136455735</v>
+        <v>42.18283711851126</v>
       </c>
       <c r="D16">
-        <v>45.55711136455735</v>
+        <v>45.64633711851126</v>
       </c>
       <c r="E16">
-        <v>5.242600000000001</v>
+        <v>5.723500000000001</v>
       </c>
       <c r="F16">
-        <v>6.732600000000001</v>
+        <v>7.213500000000002</v>
       </c>
       <c r="G16">
         <v>3.75</v>
@@ -2727,28 +2727,28 @@
         <v>5.37</v>
       </c>
       <c r="M16">
-        <v>0.3386497800000001</v>
+        <v>0.3628390500000001</v>
       </c>
       <c r="N16">
-        <v>5.03135022</v>
+        <v>5.00716095</v>
       </c>
       <c r="O16">
-        <v>1.1572105506</v>
+        <v>1.1516470185</v>
       </c>
       <c r="P16">
-        <v>3.8741396694</v>
+        <v>3.8555139315</v>
       </c>
       <c r="Q16">
-        <v>4.434139669399999</v>
+        <v>4.4155139315</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08862613191683893</v>
+        <v>0.08902699404897571</v>
       </c>
       <c r="T16">
-        <v>0.662506640411425</v>
+        <v>0.6687078501061456</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.85708988206046</v>
+        <v>14.79995055658976</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08148259494162935</v>
+        <v>0.08132437643477719</v>
       </c>
       <c r="C17">
-        <v>42.18283711851126</v>
+        <v>41.79151306403718</v>
       </c>
       <c r="D17">
-        <v>45.64633711851126</v>
+        <v>45.73591306403718</v>
       </c>
       <c r="E17">
-        <v>5.7235</v>
+        <v>6.204400000000001</v>
       </c>
       <c r="F17">
-        <v>7.2135</v>
+        <v>7.694400000000001</v>
       </c>
       <c r="G17">
         <v>3.75</v>
@@ -2809,28 +2809,28 @@
         <v>5.37</v>
       </c>
       <c r="M17">
-        <v>0.36283905</v>
+        <v>0.38702832</v>
       </c>
       <c r="N17">
-        <v>5.00716095</v>
+        <v>4.98297168</v>
       </c>
       <c r="O17">
-        <v>1.1516470185</v>
+        <v>1.1460834864</v>
       </c>
       <c r="P17">
-        <v>3.8555139315</v>
+        <v>3.8368881936</v>
       </c>
       <c r="Q17">
-        <v>4.4155139315</v>
+        <v>4.3968881936</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08902699404897571</v>
+        <v>0.0894374005175919</v>
       </c>
       <c r="T17">
-        <v>0.6687078501061456</v>
+        <v>0.6750567076507404</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.79995055658976</v>
+        <v>13.8749536468029</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08132437643477719</v>
+        <v>0.08116615792792505</v>
       </c>
       <c r="C18">
-        <v>41.79151306403718</v>
+        <v>41.40054126682681</v>
       </c>
       <c r="D18">
-        <v>45.73591306403718</v>
+        <v>45.82584126682681</v>
       </c>
       <c r="E18">
-        <v>6.204400000000001</v>
+        <v>6.685300000000002</v>
       </c>
       <c r="F18">
-        <v>7.694400000000001</v>
+        <v>8.175300000000002</v>
       </c>
       <c r="G18">
         <v>3.75</v>
@@ -2891,28 +2891,28 @@
         <v>5.37</v>
       </c>
       <c r="M18">
-        <v>0.38702832</v>
+        <v>0.4112175900000001</v>
       </c>
       <c r="N18">
-        <v>4.98297168</v>
+        <v>4.95878241</v>
       </c>
       <c r="O18">
-        <v>1.1460834864</v>
+        <v>1.1405199543</v>
       </c>
       <c r="P18">
-        <v>3.8368881936</v>
+        <v>3.8182624557</v>
       </c>
       <c r="Q18">
-        <v>4.3968881936</v>
+        <v>4.3782624557</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0894374005175919</v>
+        <v>0.08985769629870488</v>
       </c>
       <c r="T18">
-        <v>0.6750567076507404</v>
+        <v>0.6815585497144822</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.8749536468029</v>
+        <v>13.05877990287332</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08116615792792505</v>
+        <v>0.0812158394210729</v>
       </c>
       <c r="C19">
-        <v>41.40054126682681</v>
+        <v>40.89136524497094</v>
       </c>
       <c r="D19">
-        <v>45.82584126682681</v>
+        <v>45.79756524497094</v>
       </c>
       <c r="E19">
-        <v>6.685300000000002</v>
+        <v>7.166200000000002</v>
       </c>
       <c r="F19">
-        <v>8.175300000000002</v>
+        <v>8.656200000000002</v>
       </c>
       <c r="G19">
         <v>3.75</v>
@@ -2973,45 +2973,45 @@
         <v>5.37</v>
       </c>
       <c r="M19">
-        <v>0.4112175900000001</v>
+        <v>0.4483911600000001</v>
       </c>
       <c r="N19">
-        <v>4.95878241</v>
+        <v>4.92160884</v>
       </c>
       <c r="O19">
-        <v>1.1405199543</v>
+        <v>1.1319700332</v>
       </c>
       <c r="P19">
-        <v>3.8182624557</v>
+        <v>3.7896388068</v>
       </c>
       <c r="Q19">
-        <v>4.3782624557</v>
+        <v>4.3496388068</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08985769629870488</v>
+        <v>0.09028824319643036</v>
       </c>
       <c r="T19">
-        <v>0.6815585497144822</v>
+        <v>0.6882189732919736</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.23</v>
       </c>
       <c r="W19">
-        <v>0.038731</v>
+        <v>0.039886</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.05877990287332</v>
+        <v>11.9761504664811</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08121583942107291</v>
+        <v>0.08106917091422075</v>
       </c>
       <c r="C20">
-        <v>40.89136524497094</v>
+        <v>40.49404177001973</v>
       </c>
       <c r="D20">
-        <v>45.79756524497094</v>
+        <v>45.88114177001974</v>
       </c>
       <c r="E20">
-        <v>7.1662</v>
+        <v>7.6471</v>
       </c>
       <c r="F20">
-        <v>8.6562</v>
+        <v>9.1371</v>
       </c>
       <c r="G20">
         <v>3.75</v>
@@ -3055,28 +3055,28 @@
         <v>5.37</v>
       </c>
       <c r="M20">
-        <v>0.44839116</v>
+        <v>0.47330178</v>
       </c>
       <c r="N20">
-        <v>4.92160884</v>
+        <v>4.89669822</v>
       </c>
       <c r="O20">
-        <v>1.1319700332</v>
+        <v>1.1262405906</v>
       </c>
       <c r="P20">
-        <v>3.7896388068</v>
+        <v>3.7704576294</v>
       </c>
       <c r="Q20">
-        <v>4.3496388068</v>
+        <v>4.3304576294</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09028824319643036</v>
+        <v>0.09072942088175401</v>
       </c>
       <c r="T20">
-        <v>0.6882189732919736</v>
+        <v>0.6950438517726131</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.9761504664811</v>
+        <v>11.34582675771893</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08106917091422075</v>
+        <v>0.08092250240736862</v>
       </c>
       <c r="C21">
-        <v>40.49404177001973</v>
+        <v>40.09702389235876</v>
       </c>
       <c r="D21">
-        <v>45.88114177001974</v>
+        <v>45.96502389235876</v>
       </c>
       <c r="E21">
-        <v>7.6471</v>
+        <v>8.128000000000002</v>
       </c>
       <c r="F21">
-        <v>9.1371</v>
+        <v>9.618000000000002</v>
       </c>
       <c r="G21">
         <v>3.75</v>
@@ -3137,28 +3137,28 @@
         <v>5.37</v>
       </c>
       <c r="M21">
-        <v>0.47330178</v>
+        <v>0.4982124000000001</v>
       </c>
       <c r="N21">
-        <v>4.89669822</v>
+        <v>4.8717876</v>
       </c>
       <c r="O21">
-        <v>1.1262405906</v>
+        <v>1.120511148</v>
       </c>
       <c r="P21">
-        <v>3.7704576294</v>
+        <v>3.751276452</v>
       </c>
       <c r="Q21">
-        <v>4.3304576294</v>
+        <v>4.311276452</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09072942088175401</v>
+        <v>0.09118162800921076</v>
       </c>
       <c r="T21">
-        <v>0.6950438517726131</v>
+        <v>0.7020393522152685</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.34582675771893</v>
+        <v>10.77853541983299</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08092250240736862</v>
+        <v>0.08077583390051647</v>
       </c>
       <c r="C22">
-        <v>40.09702389235876</v>
+        <v>39.70031329118124</v>
       </c>
       <c r="D22">
-        <v>45.96502389235876</v>
+        <v>46.04921329118124</v>
       </c>
       <c r="E22">
-        <v>8.128000000000002</v>
+        <v>8.608900000000002</v>
       </c>
       <c r="F22">
-        <v>9.618000000000002</v>
+        <v>10.0989</v>
       </c>
       <c r="G22">
         <v>3.75</v>
@@ -3219,28 +3219,28 @@
         <v>5.37</v>
       </c>
       <c r="M22">
-        <v>0.4982124000000001</v>
+        <v>0.5231230200000001</v>
       </c>
       <c r="N22">
-        <v>4.8717876</v>
+        <v>4.84687698</v>
       </c>
       <c r="O22">
-        <v>1.120511148</v>
+        <v>1.1147817054</v>
       </c>
       <c r="P22">
-        <v>3.751276452</v>
+        <v>3.7320952746</v>
       </c>
       <c r="Q22">
-        <v>4.311276452</v>
+        <v>4.292095274599999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09118162800921076</v>
+        <v>0.09164528341837527</v>
       </c>
       <c r="T22">
-        <v>0.7020393522152685</v>
+        <v>0.7092119539349533</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.77853541983299</v>
+        <v>10.26527182841237</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08077583390051647</v>
+        <v>0.08091714539366433</v>
       </c>
       <c r="C23">
-        <v>39.70031329118124</v>
+        <v>39.13829346257012</v>
       </c>
       <c r="D23">
-        <v>46.04921329118124</v>
+        <v>45.96809346257012</v>
       </c>
       <c r="E23">
-        <v>8.6089</v>
+        <v>9.0898</v>
       </c>
       <c r="F23">
-        <v>10.0989</v>
+        <v>10.5798</v>
       </c>
       <c r="G23">
         <v>3.75</v>
@@ -3301,45 +3301,45 @@
         <v>5.37</v>
       </c>
       <c r="M23">
-        <v>0.52312302</v>
+        <v>0.5660193</v>
       </c>
       <c r="N23">
-        <v>4.84687698</v>
+        <v>4.8039807</v>
       </c>
       <c r="O23">
-        <v>1.1147817054</v>
+        <v>1.104915561</v>
       </c>
       <c r="P23">
-        <v>3.7320952746</v>
+        <v>3.699065139</v>
       </c>
       <c r="Q23">
-        <v>4.292095274599999</v>
+        <v>4.259065139</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09164528341837527</v>
+        <v>0.09212082742777478</v>
       </c>
       <c r="T23">
-        <v>0.7092119539349533</v>
+        <v>0.7165684685192453</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.23</v>
       </c>
       <c r="W23">
-        <v>0.039886</v>
+        <v>0.041195</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>10.26527182841237</v>
+        <v>9.487309001654184</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08091714539366433</v>
+        <v>0.08078356688681218</v>
       </c>
       <c r="C24">
-        <v>39.13829346257012</v>
+        <v>38.73406676795246</v>
       </c>
       <c r="D24">
-        <v>45.96809346257012</v>
+        <v>46.04476676795246</v>
       </c>
       <c r="E24">
-        <v>9.0898</v>
+        <v>9.5707</v>
       </c>
       <c r="F24">
-        <v>10.5798</v>
+        <v>11.0607</v>
       </c>
       <c r="G24">
         <v>3.75</v>
@@ -3383,28 +3383,28 @@
         <v>5.37</v>
       </c>
       <c r="M24">
-        <v>0.5660193</v>
+        <v>0.5917474500000001</v>
       </c>
       <c r="N24">
-        <v>4.8039807</v>
+        <v>4.77825255</v>
       </c>
       <c r="O24">
-        <v>1.104915561</v>
+        <v>1.0989980865</v>
       </c>
       <c r="P24">
-        <v>3.699065139</v>
+        <v>3.6792544635</v>
       </c>
       <c r="Q24">
-        <v>4.259065139</v>
+        <v>4.2392544635</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09212082742777478</v>
+        <v>0.0926087232296262</v>
       </c>
       <c r="T24">
-        <v>0.7165684685192453</v>
+        <v>0.724116061404428</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.487309001654184</v>
+        <v>9.074817305930088</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08078356688681218</v>
+        <v>0.08064998837996003</v>
       </c>
       <c r="C25">
-        <v>38.73406676795246</v>
+        <v>38.33009627790368</v>
       </c>
       <c r="D25">
-        <v>46.04476676795246</v>
+        <v>46.12169627790368</v>
       </c>
       <c r="E25">
-        <v>9.5707</v>
+        <v>10.0516</v>
       </c>
       <c r="F25">
-        <v>11.0607</v>
+        <v>11.5416</v>
       </c>
       <c r="G25">
         <v>3.75</v>
@@ -3465,28 +3465,28 @@
         <v>5.37</v>
       </c>
       <c r="M25">
-        <v>0.5917474500000001</v>
+        <v>0.6174756000000001</v>
       </c>
       <c r="N25">
-        <v>4.77825255</v>
+        <v>4.7525244</v>
       </c>
       <c r="O25">
-        <v>1.0989980865</v>
+        <v>1.093080612</v>
       </c>
       <c r="P25">
-        <v>3.6792544635</v>
+        <v>3.659443788</v>
       </c>
       <c r="Q25">
-        <v>4.2392544635</v>
+        <v>4.219443788</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0926087232296262</v>
+        <v>0.09310945839468424</v>
       </c>
       <c r="T25">
-        <v>0.724116061404428</v>
+        <v>0.7318622751550101</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.074817305930088</v>
+        <v>8.696699918183</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08064998837996003</v>
+        <v>0.08051640987310787</v>
       </c>
       <c r="C26">
-        <v>38.33009627790368</v>
+        <v>37.92638327873785</v>
       </c>
       <c r="D26">
-        <v>46.12169627790368</v>
+        <v>46.19888327873785</v>
       </c>
       <c r="E26">
-        <v>10.0516</v>
+        <v>10.5325</v>
       </c>
       <c r="F26">
-        <v>11.5416</v>
+        <v>12.0225</v>
       </c>
       <c r="G26">
         <v>3.75</v>
@@ -3547,28 +3547,28 @@
         <v>5.37</v>
       </c>
       <c r="M26">
-        <v>0.6174756</v>
+        <v>0.6432037500000001</v>
       </c>
       <c r="N26">
-        <v>4.7525244</v>
+        <v>4.72679625</v>
       </c>
       <c r="O26">
-        <v>1.093080612</v>
+        <v>1.0871631375</v>
       </c>
       <c r="P26">
-        <v>3.659443788</v>
+        <v>3.639633112499999</v>
       </c>
       <c r="Q26">
-        <v>4.219443788</v>
+        <v>4.199633112499999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09310945839468424</v>
+        <v>0.09362354649747717</v>
       </c>
       <c r="T26">
-        <v>0.7318622751550101</v>
+        <v>0.7398150546056079</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.696699918183002</v>
+        <v>8.34883192145568</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08051640987310787</v>
+        <v>0.08038283136625574</v>
       </c>
       <c r="C27">
-        <v>37.92638327873785</v>
+        <v>37.52292906539432</v>
       </c>
       <c r="D27">
-        <v>46.19888327873785</v>
+        <v>46.27632906539431</v>
       </c>
       <c r="E27">
-        <v>10.5325</v>
+        <v>11.0134</v>
       </c>
       <c r="F27">
-        <v>12.0225</v>
+        <v>12.5034</v>
       </c>
       <c r="G27">
         <v>3.75</v>
@@ -3629,28 +3629,28 @@
         <v>5.37</v>
       </c>
       <c r="M27">
-        <v>0.6432037500000001</v>
+        <v>0.6689319</v>
       </c>
       <c r="N27">
-        <v>4.72679625</v>
+        <v>4.701068100000001</v>
       </c>
       <c r="O27">
-        <v>1.0871631375</v>
+        <v>1.081245663</v>
       </c>
       <c r="P27">
-        <v>3.639633112499999</v>
+        <v>3.619822437</v>
       </c>
       <c r="Q27">
-        <v>4.199633112499999</v>
+        <v>4.179822437</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09362354649747717</v>
+        <v>0.09415152887331855</v>
       </c>
       <c r="T27">
-        <v>0.7398150546056079</v>
+        <v>0.747982774041357</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.34883192145568</v>
+        <v>8.027723001399695</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08038283136625574</v>
+        <v>0.08024925285940358</v>
       </c>
       <c r="C28">
-        <v>37.52292906539432</v>
+        <v>37.11973494151013</v>
       </c>
       <c r="D28">
-        <v>46.27632906539431</v>
+        <v>46.35403494151013</v>
       </c>
       <c r="E28">
-        <v>11.0134</v>
+        <v>11.4943</v>
       </c>
       <c r="F28">
-        <v>12.5034</v>
+        <v>12.9843</v>
       </c>
       <c r="G28">
         <v>3.75</v>
@@ -3711,28 +3711,28 @@
         <v>5.37</v>
       </c>
       <c r="M28">
-        <v>0.6689319</v>
+        <v>0.6946600500000001</v>
       </c>
       <c r="N28">
-        <v>4.701068100000001</v>
+        <v>4.67533995</v>
       </c>
       <c r="O28">
-        <v>1.081245663</v>
+        <v>1.0753281885</v>
       </c>
       <c r="P28">
-        <v>3.619822437</v>
+        <v>3.6000117615</v>
       </c>
       <c r="Q28">
-        <v>4.179822437</v>
+        <v>4.1600117615</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09415152887331855</v>
+        <v>0.09469397651973094</v>
       </c>
       <c r="T28">
-        <v>0.747982774041357</v>
+        <v>0.7563742666123321</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.027723001399695</v>
+        <v>7.730399927273778</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08024925285940358</v>
+        <v>0.08028815435255143</v>
       </c>
       <c r="C29">
-        <v>37.11973494151013</v>
+        <v>36.61617807399088</v>
       </c>
       <c r="D29">
-        <v>46.35403494151013</v>
+        <v>46.33137807399088</v>
       </c>
       <c r="E29">
-        <v>11.4943</v>
+        <v>11.9752</v>
       </c>
       <c r="F29">
-        <v>12.9843</v>
+        <v>13.4652</v>
       </c>
       <c r="G29">
         <v>3.75</v>
@@ -3793,45 +3793,45 @@
         <v>5.37</v>
       </c>
       <c r="M29">
-        <v>0.6946600500000001</v>
+        <v>0.7311603600000002</v>
       </c>
       <c r="N29">
-        <v>4.67533995</v>
+        <v>4.63883964</v>
       </c>
       <c r="O29">
-        <v>1.0753281885</v>
+        <v>1.0669331172</v>
       </c>
       <c r="P29">
-        <v>3.6000117615</v>
+        <v>3.5719065228</v>
       </c>
       <c r="Q29">
-        <v>4.1600117615</v>
+        <v>4.1319065228</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09469397651973094</v>
+        <v>0.09525149215632145</v>
       </c>
       <c r="T29">
-        <v>0.7563742666123321</v>
+        <v>0.7649988561991676</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.23</v>
       </c>
       <c r="W29">
-        <v>0.041195</v>
+        <v>0.041811</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.730399927273778</v>
+        <v>7.344490065079565</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08028815435255143</v>
+        <v>0.0801607358456993</v>
       </c>
       <c r="C30">
-        <v>36.61617807399088</v>
+        <v>36.20957136929096</v>
       </c>
       <c r="D30">
-        <v>46.33137807399088</v>
+        <v>46.40567136929096</v>
       </c>
       <c r="E30">
-        <v>11.9752</v>
+        <v>12.4561</v>
       </c>
       <c r="F30">
-        <v>13.4652</v>
+        <v>13.9461</v>
       </c>
       <c r="G30">
         <v>3.75</v>
@@ -3875,28 +3875,28 @@
         <v>5.37</v>
       </c>
       <c r="M30">
-        <v>0.7311603600000002</v>
+        <v>0.7572732300000001</v>
       </c>
       <c r="N30">
-        <v>4.63883964</v>
+        <v>4.61272677</v>
       </c>
       <c r="O30">
-        <v>1.0669331172</v>
+        <v>1.0609271571</v>
       </c>
       <c r="P30">
-        <v>3.5719065228</v>
+        <v>3.5517996129</v>
       </c>
       <c r="Q30">
-        <v>4.1319065228</v>
+        <v>4.1117996129</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09525149215632145</v>
+        <v>0.09582471245873139</v>
       </c>
       <c r="T30">
-        <v>0.7649988561991676</v>
+        <v>0.7738663919715477</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.344490065079565</v>
+        <v>7.091231786973375</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08016073584569929</v>
+        <v>0.08003331733884714</v>
       </c>
       <c r="C31">
-        <v>36.20957136929096</v>
+        <v>35.80320330884425</v>
       </c>
       <c r="D31">
-        <v>46.40567136929096</v>
+        <v>46.48020330884425</v>
       </c>
       <c r="E31">
-        <v>12.4561</v>
+        <v>12.937</v>
       </c>
       <c r="F31">
-        <v>13.9461</v>
+        <v>14.427</v>
       </c>
       <c r="G31">
         <v>3.75</v>
@@ -3957,28 +3957,28 @@
         <v>5.37</v>
       </c>
       <c r="M31">
-        <v>0.75727323</v>
+        <v>0.7833861</v>
       </c>
       <c r="N31">
-        <v>4.61272677</v>
+        <v>4.5866139</v>
       </c>
       <c r="O31">
-        <v>1.0609271571</v>
+        <v>1.054921197</v>
       </c>
       <c r="P31">
-        <v>3.5517996129</v>
+        <v>3.531692703</v>
       </c>
       <c r="Q31">
-        <v>4.1117996129</v>
+        <v>4.091692703</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09582471245873139</v>
+        <v>0.09641431048406734</v>
       </c>
       <c r="T31">
-        <v>0.7738663919715477</v>
+        <v>0.782987285908853</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.091231786973376</v>
+        <v>6.854857394074263</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08003331733884714</v>
+        <v>0.07990589883199498</v>
       </c>
       <c r="C32">
-        <v>35.80320330884425</v>
+        <v>35.39707504435691</v>
       </c>
       <c r="D32">
-        <v>46.48020330884425</v>
+        <v>46.55497504435691</v>
       </c>
       <c r="E32">
-        <v>12.937</v>
+        <v>13.4179</v>
       </c>
       <c r="F32">
-        <v>14.427</v>
+        <v>14.9079</v>
       </c>
       <c r="G32">
         <v>3.75</v>
@@ -4039,28 +4039,28 @@
         <v>5.37</v>
       </c>
       <c r="M32">
-        <v>0.7833861</v>
+        <v>0.8094989700000002</v>
       </c>
       <c r="N32">
-        <v>4.5866139</v>
+        <v>4.56050103</v>
       </c>
       <c r="O32">
-        <v>1.054921197</v>
+        <v>1.0489152369</v>
       </c>
       <c r="P32">
-        <v>3.531692703</v>
+        <v>3.5115857931</v>
       </c>
       <c r="Q32">
-        <v>4.091692703</v>
+        <v>4.0715857931</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09641431048406734</v>
+        <v>0.09702099830723912</v>
       </c>
       <c r="T32">
-        <v>0.782987285908853</v>
+        <v>0.7923725535834715</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.854857394074263</v>
+        <v>6.63373296200735</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07990589883199498</v>
+        <v>0.07977848032514286</v>
       </c>
       <c r="C33">
-        <v>35.39707504435691</v>
+        <v>34.99118773495785</v>
       </c>
       <c r="D33">
-        <v>46.55497504435691</v>
+        <v>46.62998773495785</v>
       </c>
       <c r="E33">
-        <v>13.4179</v>
+        <v>13.8988</v>
       </c>
       <c r="F33">
-        <v>14.9079</v>
+        <v>15.3888</v>
       </c>
       <c r="G33">
         <v>3.75</v>
@@ -4121,28 +4121,28 @@
         <v>5.37</v>
       </c>
       <c r="M33">
-        <v>0.8094989700000002</v>
+        <v>0.8356118400000001</v>
       </c>
       <c r="N33">
-        <v>4.56050103</v>
+        <v>4.53438816</v>
       </c>
       <c r="O33">
-        <v>1.0489152369</v>
+        <v>1.0429092768</v>
       </c>
       <c r="P33">
-        <v>3.5115857931</v>
+        <v>3.4914788832</v>
       </c>
       <c r="Q33">
-        <v>4.0715857931</v>
+        <v>4.0514788832</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09702099830723912</v>
+        <v>0.09764552988991596</v>
       </c>
       <c r="T33">
-        <v>0.7923725535834715</v>
+        <v>0.8020338585426375</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.63373296200735</v>
+        <v>6.426428806944621</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07977848032514286</v>
+        <v>0.07965106181829071</v>
       </c>
       <c r="C34">
-        <v>34.99118773495785</v>
+        <v>34.58554254725883</v>
       </c>
       <c r="D34">
-        <v>46.62998773495785</v>
+        <v>46.70524254725883</v>
       </c>
       <c r="E34">
-        <v>13.8988</v>
+        <v>14.3797</v>
       </c>
       <c r="F34">
-        <v>15.3888</v>
+        <v>15.8697</v>
       </c>
       <c r="G34">
         <v>3.75</v>
@@ -4203,28 +4203,28 @@
         <v>5.37</v>
       </c>
       <c r="M34">
-        <v>0.8356118400000001</v>
+        <v>0.8617247100000001</v>
       </c>
       <c r="N34">
-        <v>4.53438816</v>
+        <v>4.50827529</v>
       </c>
       <c r="O34">
-        <v>1.0429092768</v>
+        <v>1.0369033167</v>
       </c>
       <c r="P34">
-        <v>3.4914788832</v>
+        <v>3.4713719733</v>
       </c>
       <c r="Q34">
-        <v>4.0514788832</v>
+        <v>4.0313719733</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09764552988991596</v>
+        <v>0.09828870420640404</v>
       </c>
       <c r="T34">
-        <v>0.8020338585426375</v>
+        <v>0.8119835606647637</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.426428806944621</v>
+        <v>6.231688540067512</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07965106181829071</v>
+        <v>0.07978544331143854</v>
       </c>
       <c r="C35">
-        <v>34.58554254725883</v>
+        <v>34.02528230414946</v>
       </c>
       <c r="D35">
-        <v>46.70524254725883</v>
+        <v>46.62588230414946</v>
       </c>
       <c r="E35">
-        <v>14.3797</v>
+        <v>14.8606</v>
       </c>
       <c r="F35">
-        <v>15.8697</v>
+        <v>16.3506</v>
       </c>
       <c r="G35">
         <v>3.75</v>
@@ -4285,45 +4285,45 @@
         <v>5.37</v>
       </c>
       <c r="M35">
-        <v>0.8617247100000001</v>
+        <v>0.9041881800000002</v>
       </c>
       <c r="N35">
-        <v>4.50827529</v>
+        <v>4.46581182</v>
       </c>
       <c r="O35">
-        <v>1.0369033167</v>
+        <v>1.0271367186</v>
       </c>
       <c r="P35">
-        <v>3.4713719733</v>
+        <v>3.4386751014</v>
       </c>
       <c r="Q35">
-        <v>4.0313719733</v>
+        <v>3.998675101399999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09828870420640404</v>
+        <v>0.09895136865369478</v>
       </c>
       <c r="T35">
-        <v>0.8119835606647637</v>
+        <v>0.822234768911803</v>
       </c>
       <c r="U35">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.23</v>
       </c>
       <c r="W35">
-        <v>0.041811</v>
+        <v>0.042581</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.231688540067512</v>
+        <v>5.939029196333886</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07978544331143854</v>
+        <v>0.07966572480458639</v>
       </c>
       <c r="C36">
-        <v>34.02528230414946</v>
+        <v>33.61507005591845</v>
       </c>
       <c r="D36">
-        <v>46.62588230414946</v>
+        <v>46.69657005591845</v>
       </c>
       <c r="E36">
-        <v>14.8606</v>
+        <v>15.3415</v>
       </c>
       <c r="F36">
-        <v>16.3506</v>
+        <v>16.8315</v>
       </c>
       <c r="G36">
         <v>3.75</v>
@@ -4367,28 +4367,28 @@
         <v>5.37</v>
       </c>
       <c r="M36">
-        <v>0.9041881800000002</v>
+        <v>0.9307819500000002</v>
       </c>
       <c r="N36">
-        <v>4.46581182</v>
+        <v>4.43921805</v>
       </c>
       <c r="O36">
-        <v>1.0271367186</v>
+        <v>1.0210201515</v>
       </c>
       <c r="P36">
-        <v>3.4386751014</v>
+        <v>3.4181978985</v>
       </c>
       <c r="Q36">
-        <v>3.998675101399999</v>
+        <v>3.978197898499999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09895136865369478</v>
+        <v>0.09963442277628679</v>
       </c>
       <c r="T36">
-        <v>0.822234768911803</v>
+        <v>0.8328013989510588</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.939029196333886</v>
+        <v>5.769342647867203</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07966572480458639</v>
+        <v>0.07954600629773426</v>
       </c>
       <c r="C37">
-        <v>33.61507005591845</v>
+        <v>33.20507246722428</v>
       </c>
       <c r="D37">
-        <v>46.69657005591845</v>
+        <v>46.76747246722429</v>
       </c>
       <c r="E37">
-        <v>15.3415</v>
+        <v>15.8224</v>
       </c>
       <c r="F37">
-        <v>16.8315</v>
+        <v>17.3124</v>
       </c>
       <c r="G37">
         <v>3.75</v>
@@ -4449,28 +4449,28 @@
         <v>5.37</v>
       </c>
       <c r="M37">
-        <v>0.9307819500000002</v>
+        <v>0.9573757200000003</v>
       </c>
       <c r="N37">
-        <v>4.43921805</v>
+        <v>4.41262428</v>
       </c>
       <c r="O37">
-        <v>1.0210201515</v>
+        <v>1.0149035844</v>
       </c>
       <c r="P37">
-        <v>3.4181978985</v>
+        <v>3.3977206956</v>
       </c>
       <c r="Q37">
-        <v>3.978197898499999</v>
+        <v>3.9577206956</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09963442277628679</v>
+        <v>0.1003388223402098</v>
       </c>
       <c r="T37">
-        <v>0.8328013989510588</v>
+        <v>0.8436982361790413</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.769342647867203</v>
+        <v>5.609083129870892</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07954600629773426</v>
+        <v>0.07942628779088212</v>
       </c>
       <c r="C38">
-        <v>33.20507246722428</v>
+        <v>32.7952905173481</v>
       </c>
       <c r="D38">
-        <v>46.76747246722429</v>
+        <v>46.8385905173481</v>
       </c>
       <c r="E38">
-        <v>15.8224</v>
+        <v>16.3033</v>
       </c>
       <c r="F38">
-        <v>17.3124</v>
+        <v>17.7933</v>
       </c>
       <c r="G38">
         <v>3.75</v>
@@ -4531,28 +4531,28 @@
         <v>5.37</v>
       </c>
       <c r="M38">
-        <v>0.95737572</v>
+        <v>0.9839694900000001</v>
       </c>
       <c r="N38">
-        <v>4.41262428</v>
+        <v>4.38603051</v>
       </c>
       <c r="O38">
-        <v>1.0149035844</v>
+        <v>1.0087870173</v>
       </c>
       <c r="P38">
-        <v>3.3977206956</v>
+        <v>3.3772434927</v>
       </c>
       <c r="Q38">
-        <v>3.9577206956</v>
+        <v>3.9372434927</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1003388223402098</v>
+        <v>0.101065583795051</v>
       </c>
       <c r="T38">
-        <v>0.8436982361790413</v>
+        <v>0.8549410047475947</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.609083129870894</v>
+        <v>5.457486288523032</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07942628779088212</v>
+        <v>0.07930656928402996</v>
       </c>
       <c r="C39">
-        <v>32.7952905173481</v>
+        <v>32.38572519153676</v>
       </c>
       <c r="D39">
-        <v>46.8385905173481</v>
+        <v>46.90992519153676</v>
       </c>
       <c r="E39">
-        <v>16.3033</v>
+        <v>16.7842</v>
       </c>
       <c r="F39">
-        <v>17.7933</v>
+        <v>18.2742</v>
       </c>
       <c r="G39">
         <v>3.75</v>
@@ -4613,28 +4613,28 @@
         <v>5.37</v>
       </c>
       <c r="M39">
-        <v>0.9839694900000001</v>
+        <v>1.01056326</v>
       </c>
       <c r="N39">
-        <v>4.38603051</v>
+        <v>4.35943674</v>
       </c>
       <c r="O39">
-        <v>1.0087870173</v>
+        <v>1.0026704502</v>
       </c>
       <c r="P39">
-        <v>3.3772434927</v>
+        <v>3.356766289799999</v>
       </c>
       <c r="Q39">
-        <v>3.9372434927</v>
+        <v>3.916766289799999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.101065583795051</v>
+        <v>0.1018157891677903</v>
       </c>
       <c r="T39">
-        <v>0.8549410047475947</v>
+        <v>0.8665464432699723</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.457486288523032</v>
+        <v>5.31386822829874</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07930656928402996</v>
+        <v>0.07918685077717783</v>
       </c>
       <c r="C40">
-        <v>32.38572519153676</v>
+        <v>31.97637748104834</v>
       </c>
       <c r="D40">
-        <v>46.90992519153676</v>
+        <v>46.98147748104834</v>
       </c>
       <c r="E40">
-        <v>16.7842</v>
+        <v>17.2651</v>
       </c>
       <c r="F40">
-        <v>18.2742</v>
+        <v>18.7551</v>
       </c>
       <c r="G40">
         <v>3.75</v>
@@ -4695,28 +4695,28 @@
         <v>5.37</v>
       </c>
       <c r="M40">
-        <v>1.01056326</v>
+        <v>1.03715703</v>
       </c>
       <c r="N40">
-        <v>4.35943674</v>
+        <v>4.33284297</v>
       </c>
       <c r="O40">
-        <v>1.0026704502</v>
+        <v>0.9965538831</v>
       </c>
       <c r="P40">
-        <v>3.356766289799999</v>
+        <v>3.3362890869</v>
       </c>
       <c r="Q40">
-        <v>3.916766289799999</v>
+        <v>3.8962890869</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1018157891677903</v>
+        <v>0.1025905914379964</v>
       </c>
       <c r="T40">
-        <v>0.8665464432699723</v>
+        <v>0.8785323879734117</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.31386822829874</v>
+        <v>5.177615196803901</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07918685077717783</v>
+        <v>0.07906713227032568</v>
       </c>
       <c r="C41">
-        <v>31.97637748104834</v>
+        <v>31.56724838319813</v>
       </c>
       <c r="D41">
-        <v>46.98147748104834</v>
+        <v>47.05324838319814</v>
       </c>
       <c r="E41">
-        <v>17.2651</v>
+        <v>17.74600000000001</v>
       </c>
       <c r="F41">
-        <v>18.7551</v>
+        <v>19.236</v>
       </c>
       <c r="G41">
         <v>3.75</v>
@@ -4777,28 +4777,28 @@
         <v>5.37</v>
       </c>
       <c r="M41">
-        <v>1.03715703</v>
+        <v>1.0637508</v>
       </c>
       <c r="N41">
-        <v>4.33284297</v>
+        <v>4.3062492</v>
       </c>
       <c r="O41">
-        <v>0.9965538831</v>
+        <v>0.9904373160000001</v>
       </c>
       <c r="P41">
-        <v>3.3362890869</v>
+        <v>3.315811884</v>
       </c>
       <c r="Q41">
-        <v>3.8962890869</v>
+        <v>3.875811884</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1025905914379964</v>
+        <v>0.1033912204505428</v>
       </c>
       <c r="T41">
-        <v>0.8785323879734117</v>
+        <v>0.8909178641669656</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.177615196803901</v>
+        <v>5.048174816883803</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07906713227032568</v>
+        <v>0.07894741376347353</v>
       </c>
       <c r="C42">
-        <v>31.56724838319813</v>
+        <v>31.15833890140485</v>
       </c>
       <c r="D42">
-        <v>47.05324838319814</v>
+        <v>47.12523890140485</v>
       </c>
       <c r="E42">
-        <v>17.74600000000001</v>
+        <v>18.2269</v>
       </c>
       <c r="F42">
-        <v>19.236</v>
+        <v>19.7169</v>
       </c>
       <c r="G42">
         <v>3.75</v>
@@ -4859,28 +4859,28 @@
         <v>5.37</v>
       </c>
       <c r="M42">
-        <v>1.0637508</v>
+        <v>1.09034457</v>
       </c>
       <c r="N42">
-        <v>4.3062492</v>
+        <v>4.27965543</v>
       </c>
       <c r="O42">
-        <v>0.9904373160000001</v>
+        <v>0.9843207489000001</v>
       </c>
       <c r="P42">
-        <v>3.315811884</v>
+        <v>3.2953346811</v>
       </c>
       <c r="Q42">
-        <v>3.875811884</v>
+        <v>3.8553346811</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1033912204505428</v>
+        <v>0.1042189894296162</v>
       </c>
       <c r="T42">
-        <v>0.8909178641669656</v>
+        <v>0.9037231870111484</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.048174816883803</v>
+        <v>4.925048601837857</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07894741376347353</v>
+        <v>0.07882769525662139</v>
       </c>
       <c r="C43">
-        <v>31.15833890140485</v>
+        <v>30.74965004523748</v>
       </c>
       <c r="D43">
-        <v>47.12523890140485</v>
+        <v>47.19745004523748</v>
       </c>
       <c r="E43">
-        <v>18.2269</v>
+        <v>18.70780000000001</v>
       </c>
       <c r="F43">
-        <v>19.7169</v>
+        <v>20.1978</v>
       </c>
       <c r="G43">
         <v>3.75</v>
@@ -4941,28 +4941,28 @@
         <v>5.37</v>
       </c>
       <c r="M43">
-        <v>1.09034457</v>
+        <v>1.11693834</v>
       </c>
       <c r="N43">
-        <v>4.27965543</v>
+        <v>4.25306166</v>
       </c>
       <c r="O43">
-        <v>0.9843207489000001</v>
+        <v>0.9782041818000001</v>
       </c>
       <c r="P43">
-        <v>3.2953346811</v>
+        <v>3.2748574782</v>
       </c>
       <c r="Q43">
-        <v>3.8553346811</v>
+        <v>3.8348574782</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1042189894296162</v>
+        <v>0.1050753021665886</v>
       </c>
       <c r="T43">
-        <v>0.9037231870111484</v>
+        <v>0.9169700727120272</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.925048601837857</v>
+        <v>4.807785539889336</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07882769525662139</v>
+        <v>0.07870797674976923</v>
       </c>
       <c r="C44">
-        <v>30.74965004523748</v>
+        <v>30.3411828304625</v>
       </c>
       <c r="D44">
-        <v>47.19745004523748</v>
+        <v>47.26988283046251</v>
       </c>
       <c r="E44">
-        <v>18.7078</v>
+        <v>19.1887</v>
       </c>
       <c r="F44">
-        <v>20.1978</v>
+        <v>20.6787</v>
       </c>
       <c r="G44">
         <v>3.75</v>
@@ -5023,28 +5023,28 @@
         <v>5.37</v>
       </c>
       <c r="M44">
-        <v>1.11693834</v>
+        <v>1.14353211</v>
       </c>
       <c r="N44">
-        <v>4.25306166</v>
+        <v>4.22646789</v>
       </c>
       <c r="O44">
-        <v>0.9782041818000001</v>
+        <v>0.9720876147000002</v>
       </c>
       <c r="P44">
-        <v>3.2748574782</v>
+        <v>3.2543802753</v>
       </c>
       <c r="Q44">
-        <v>3.8348574782</v>
+        <v>3.8143802753</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1050753021665886</v>
+        <v>0.1059616609645074</v>
       </c>
       <c r="T44">
-        <v>0.9169700727120271</v>
+        <v>0.9306817614199543</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.807785539889337</v>
+        <v>4.695976573845399</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07870797674976923</v>
+        <v>0.0785882582429171</v>
       </c>
       <c r="C45">
-        <v>30.3411828304625</v>
+        <v>29.93293827909139</v>
       </c>
       <c r="D45">
-        <v>47.26988283046251</v>
+        <v>47.34253827909139</v>
       </c>
       <c r="E45">
-        <v>19.1887</v>
+        <v>19.6696</v>
       </c>
       <c r="F45">
-        <v>20.6787</v>
+        <v>21.1596</v>
       </c>
       <c r="G45">
         <v>3.75</v>
@@ -5105,28 +5105,28 @@
         <v>5.37</v>
       </c>
       <c r="M45">
-        <v>1.14353211</v>
+        <v>1.17012588</v>
       </c>
       <c r="N45">
-        <v>4.22646789</v>
+        <v>4.19987412</v>
       </c>
       <c r="O45">
-        <v>0.9720876147000002</v>
+        <v>0.9659710476000002</v>
       </c>
       <c r="P45">
-        <v>3.2543802753</v>
+        <v>3.2339030724</v>
       </c>
       <c r="Q45">
-        <v>3.8143802753</v>
+        <v>3.7939030724</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1059616609645074</v>
+        <v>0.1068796754337805</v>
       </c>
       <c r="T45">
-        <v>0.9306817614199543</v>
+        <v>0.9448831532960218</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.695976573845399</v>
+        <v>4.589249833530731</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0785882582429171</v>
+        <v>0.07933478973606495</v>
       </c>
       <c r="C46">
-        <v>29.93293827909139</v>
+        <v>29.00259037478087</v>
       </c>
       <c r="D46">
-        <v>47.34253827909139</v>
+        <v>46.89309037478088</v>
       </c>
       <c r="E46">
-        <v>19.6696</v>
+        <v>20.1505</v>
       </c>
       <c r="F46">
-        <v>21.1596</v>
+        <v>21.6405</v>
       </c>
       <c r="G46">
         <v>3.75</v>
@@ -5187,45 +5187,45 @@
         <v>5.37</v>
       </c>
       <c r="M46">
-        <v>1.17012588</v>
+        <v>1.2508209</v>
       </c>
       <c r="N46">
-        <v>4.19987412</v>
+        <v>4.1191791</v>
       </c>
       <c r="O46">
-        <v>0.9659710476000002</v>
+        <v>0.9474111930000001</v>
       </c>
       <c r="P46">
-        <v>3.2339030724</v>
+        <v>3.171767907</v>
       </c>
       <c r="Q46">
-        <v>3.7939030724</v>
+        <v>3.731767907</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1068796754337805</v>
+        <v>0.1078310722473908</v>
       </c>
       <c r="T46">
-        <v>0.9448831532960218</v>
+        <v>0.959600959422128</v>
       </c>
       <c r="U46">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.23</v>
       </c>
       <c r="W46">
-        <v>0.042581</v>
+        <v>0.044506</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.589249833530731</v>
+        <v>4.293180582447894</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07933478973606495</v>
+        <v>0.07923432122921281</v>
       </c>
       <c r="C47">
-        <v>29.00259037478087</v>
+        <v>28.58167966425194</v>
       </c>
       <c r="D47">
-        <v>46.89309037478088</v>
+        <v>46.95307966425194</v>
       </c>
       <c r="E47">
-        <v>20.1505</v>
+        <v>20.6314</v>
       </c>
       <c r="F47">
-        <v>21.6405</v>
+        <v>22.1214</v>
       </c>
       <c r="G47">
         <v>3.75</v>
@@ -5269,28 +5269,28 @@
         <v>5.37</v>
       </c>
       <c r="M47">
-        <v>1.2508209</v>
+        <v>1.27861692</v>
       </c>
       <c r="N47">
-        <v>4.1191791</v>
+        <v>4.09138308</v>
       </c>
       <c r="O47">
-        <v>0.9474111930000001</v>
+        <v>0.9410181084</v>
       </c>
       <c r="P47">
-        <v>3.171767907</v>
+        <v>3.1503649716</v>
       </c>
       <c r="Q47">
-        <v>3.731767907</v>
+        <v>3.7103649716</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1078310722473908</v>
+        <v>0.1088177059800237</v>
       </c>
       <c r="T47">
-        <v>0.959600959422128</v>
+        <v>0.9748638694788309</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.293180582447894</v>
+        <v>4.199850569785983</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07923432122921281</v>
+        <v>0.07913385272236065</v>
       </c>
       <c r="C48">
-        <v>28.58167966425194</v>
+        <v>28.16092263625815</v>
       </c>
       <c r="D48">
-        <v>46.95307966425194</v>
+        <v>47.01322263625815</v>
       </c>
       <c r="E48">
-        <v>20.6314</v>
+        <v>21.1123</v>
       </c>
       <c r="F48">
-        <v>22.1214</v>
+        <v>22.6023</v>
       </c>
       <c r="G48">
         <v>3.75</v>
@@ -5351,28 +5351,28 @@
         <v>5.37</v>
       </c>
       <c r="M48">
-        <v>1.27861692</v>
+        <v>1.30641294</v>
       </c>
       <c r="N48">
-        <v>4.09138308</v>
+        <v>4.06358706</v>
       </c>
       <c r="O48">
-        <v>0.9410181084</v>
+        <v>0.9346250238</v>
       </c>
       <c r="P48">
-        <v>3.1503649716</v>
+        <v>3.1289620362</v>
       </c>
       <c r="Q48">
-        <v>3.7103649716</v>
+        <v>3.6889620362</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1088177059800237</v>
+        <v>0.1098415711742654</v>
       </c>
       <c r="T48">
-        <v>0.9748638694788309</v>
+        <v>0.9907027384055979</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.199850569785983</v>
+        <v>4.11049204702458</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07913385272236065</v>
+        <v>0.07903338421550851</v>
       </c>
       <c r="C49">
-        <v>28.16092263625815</v>
+        <v>27.74031988212035</v>
       </c>
       <c r="D49">
-        <v>47.01322263625815</v>
+        <v>47.07351988212036</v>
       </c>
       <c r="E49">
-        <v>21.1123</v>
+        <v>21.59320000000001</v>
       </c>
       <c r="F49">
-        <v>22.6023</v>
+        <v>23.08320000000001</v>
       </c>
       <c r="G49">
         <v>3.75</v>
@@ -5433,28 +5433,28 @@
         <v>5.37</v>
       </c>
       <c r="M49">
-        <v>1.30641294</v>
+        <v>1.33420896</v>
       </c>
       <c r="N49">
-        <v>4.06358706</v>
+        <v>4.035791039999999</v>
       </c>
       <c r="O49">
-        <v>0.9346250238</v>
+        <v>0.9282319391999999</v>
       </c>
       <c r="P49">
-        <v>3.1289620362</v>
+        <v>3.1075591008</v>
       </c>
       <c r="Q49">
-        <v>3.6889620362</v>
+        <v>3.667559100799999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1098415711742654</v>
+        <v>0.1109048157990548</v>
       </c>
       <c r="T49">
-        <v>0.9907027384055979</v>
+        <v>1.007150794598779</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.11049204702458</v>
+        <v>4.0248567960449</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07903338421550851</v>
+        <v>0.08025346570865635</v>
       </c>
       <c r="C50">
-        <v>27.74031988212036</v>
+        <v>26.53748023914969</v>
       </c>
       <c r="D50">
-        <v>47.07351988212036</v>
+        <v>46.35158023914969</v>
       </c>
       <c r="E50">
-        <v>21.5932</v>
+        <v>22.0741</v>
       </c>
       <c r="F50">
-        <v>23.0832</v>
+        <v>23.5641</v>
       </c>
       <c r="G50">
         <v>3.75</v>
@@ -5515,45 +5515,45 @@
         <v>5.37</v>
       </c>
       <c r="M50">
-        <v>1.33420896</v>
+        <v>1.44447933</v>
       </c>
       <c r="N50">
-        <v>4.035791039999999</v>
+        <v>3.92552067</v>
       </c>
       <c r="O50">
-        <v>0.9282319391999999</v>
+        <v>0.9028697541</v>
       </c>
       <c r="P50">
-        <v>3.1075591008</v>
+        <v>3.0226509159</v>
       </c>
       <c r="Q50">
-        <v>3.667559100799999</v>
+        <v>3.5826509159</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1109048157990548</v>
+        <v>0.112009756291483</v>
       </c>
       <c r="T50">
-        <v>1.007150794598779</v>
+        <v>1.024243872603458</v>
       </c>
       <c r="U50">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V50">
         <v>0.23</v>
       </c>
       <c r="W50">
-        <v>0.044506</v>
+        <v>0.047201</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.024856796044901</v>
+        <v>3.717602521872016</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08025346570865635</v>
+        <v>0.08017994720180421</v>
       </c>
       <c r="C51">
-        <v>26.53748023914969</v>
+        <v>26.09945464644974</v>
       </c>
       <c r="D51">
-        <v>46.35158023914969</v>
+        <v>46.39445464644974</v>
       </c>
       <c r="E51">
-        <v>22.0741</v>
+        <v>22.555</v>
       </c>
       <c r="F51">
-        <v>23.5641</v>
+        <v>24.045</v>
       </c>
       <c r="G51">
         <v>3.75</v>
@@ -5597,28 +5597,28 @@
         <v>5.37</v>
       </c>
       <c r="M51">
-        <v>1.44447933</v>
+        <v>1.4739585</v>
       </c>
       <c r="N51">
-        <v>3.92552067</v>
+        <v>3.8960415</v>
       </c>
       <c r="O51">
-        <v>0.9028697541</v>
+        <v>0.896089545</v>
       </c>
       <c r="P51">
-        <v>3.0226509159</v>
+        <v>2.999951955</v>
       </c>
       <c r="Q51">
-        <v>3.5826509159</v>
+        <v>3.559951954999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.112009756291483</v>
+        <v>0.1131588944036084</v>
       </c>
       <c r="T51">
-        <v>1.024243872603458</v>
+        <v>1.042020673728323</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.717602521872016</v>
+        <v>3.643250471434575</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08017994720180421</v>
+        <v>0.08010642869495208</v>
       </c>
       <c r="C52">
-        <v>26.09945464644974</v>
+        <v>25.66150844334914</v>
       </c>
       <c r="D52">
-        <v>46.39445464644974</v>
+        <v>46.43740844334914</v>
       </c>
       <c r="E52">
-        <v>22.555</v>
+        <v>23.03590000000001</v>
       </c>
       <c r="F52">
-        <v>24.045</v>
+        <v>24.5259</v>
       </c>
       <c r="G52">
         <v>3.75</v>
@@ -5679,28 +5679,28 @@
         <v>5.37</v>
       </c>
       <c r="M52">
-        <v>1.4739585</v>
+        <v>1.50343767</v>
       </c>
       <c r="N52">
-        <v>3.8960415</v>
+        <v>3.86656233</v>
       </c>
       <c r="O52">
-        <v>0.896089545</v>
+        <v>0.8893093359000001</v>
       </c>
       <c r="P52">
-        <v>2.999951955</v>
+        <v>2.9772529941</v>
       </c>
       <c r="Q52">
-        <v>3.559951954999999</v>
+        <v>3.537252994099999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1131588944036084</v>
+        <v>0.1143549361121471</v>
       </c>
       <c r="T52">
-        <v>1.042020673728323</v>
+        <v>1.060523058572571</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.643250471434575</v>
+        <v>3.571814187680956</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08010642869495208</v>
+        <v>0.08003291018809992</v>
       </c>
       <c r="C53">
-        <v>25.66150844334914</v>
+        <v>25.22364185055823</v>
       </c>
       <c r="D53">
-        <v>46.43740844334914</v>
+        <v>46.48044185055823</v>
       </c>
       <c r="E53">
-        <v>23.03590000000001</v>
+        <v>23.5168</v>
       </c>
       <c r="F53">
-        <v>24.5259</v>
+        <v>25.0068</v>
       </c>
       <c r="G53">
         <v>3.75</v>
@@ -5761,28 +5761,28 @@
         <v>5.37</v>
       </c>
       <c r="M53">
-        <v>1.50343767</v>
+        <v>1.53291684</v>
       </c>
       <c r="N53">
-        <v>3.86656233</v>
+        <v>3.83708316</v>
       </c>
       <c r="O53">
-        <v>0.8893093359000001</v>
+        <v>0.8825291268</v>
       </c>
       <c r="P53">
-        <v>2.9772529941</v>
+        <v>2.9545540332</v>
       </c>
       <c r="Q53">
-        <v>3.537252994099999</v>
+        <v>3.5145540332</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1143549361121471</v>
+        <v>0.1156008128918748</v>
       </c>
       <c r="T53">
-        <v>1.060523058572571</v>
+        <v>1.079796376118663</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.571814187680956</v>
+        <v>3.503125453302476</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08003291018809992</v>
+        <v>0.08110207168124778</v>
       </c>
       <c r="C54">
-        <v>25.22364185055823</v>
+        <v>24.1246673063025</v>
       </c>
       <c r="D54">
-        <v>46.48044185055823</v>
+        <v>45.8623673063025</v>
       </c>
       <c r="E54">
-        <v>23.5168</v>
+        <v>23.99770000000001</v>
       </c>
       <c r="F54">
-        <v>25.0068</v>
+        <v>25.4877</v>
       </c>
       <c r="G54">
         <v>3.75</v>
@@ -5843,45 +5843,45 @@
         <v>5.37</v>
       </c>
       <c r="M54">
-        <v>1.53291684</v>
+        <v>1.63376157</v>
       </c>
       <c r="N54">
-        <v>3.83708316</v>
+        <v>3.73623843</v>
       </c>
       <c r="O54">
-        <v>0.8825291268</v>
+        <v>0.8593348389</v>
       </c>
       <c r="P54">
-        <v>2.9545540332</v>
+        <v>2.8769035911</v>
       </c>
       <c r="Q54">
-        <v>3.5145540332</v>
+        <v>3.436903591099999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1156008128918748</v>
+        <v>0.1168997057047825</v>
       </c>
       <c r="T54">
-        <v>1.079796376118663</v>
+        <v>1.099889834836928</v>
       </c>
       <c r="U54">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V54">
         <v>0.23</v>
       </c>
       <c r="W54">
-        <v>0.047201</v>
+        <v>0.04935700000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.503125453302476</v>
+        <v>3.286893325566471</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08110207168124778</v>
+        <v>0.08105011317439563</v>
       </c>
       <c r="C55">
-        <v>24.1246673063025</v>
+        <v>23.67342389361187</v>
       </c>
       <c r="D55">
-        <v>45.8623673063025</v>
+        <v>45.89202389361187</v>
       </c>
       <c r="E55">
-        <v>23.99770000000001</v>
+        <v>24.4786</v>
       </c>
       <c r="F55">
-        <v>25.4877</v>
+        <v>25.9686</v>
       </c>
       <c r="G55">
         <v>3.75</v>
@@ -5925,28 +5925,28 @@
         <v>5.37</v>
       </c>
       <c r="M55">
-        <v>1.63376157</v>
+        <v>1.66458726</v>
       </c>
       <c r="N55">
-        <v>3.73623843</v>
+        <v>3.70541274</v>
       </c>
       <c r="O55">
-        <v>0.8593348389</v>
+        <v>0.8522449302</v>
       </c>
       <c r="P55">
-        <v>2.8769035911</v>
+        <v>2.8531678098</v>
       </c>
       <c r="Q55">
-        <v>3.436903591099999</v>
+        <v>3.4131678098</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1168997057047825</v>
+        <v>0.1182550721182514</v>
       </c>
       <c r="T55">
-        <v>1.099889834836928</v>
+        <v>1.120856922195118</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.286893325566471</v>
+        <v>3.226024930648574</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08105011317439563</v>
+        <v>0.08099815466754348</v>
       </c>
       <c r="C56">
-        <v>23.67342389361187</v>
+        <v>23.22221886019915</v>
       </c>
       <c r="D56">
-        <v>45.89202389361187</v>
+        <v>45.92171886019915</v>
       </c>
       <c r="E56">
-        <v>24.4786</v>
+        <v>24.95950000000001</v>
       </c>
       <c r="F56">
-        <v>25.9686</v>
+        <v>26.4495</v>
       </c>
       <c r="G56">
         <v>3.75</v>
@@ -6007,28 +6007,28 @@
         <v>5.37</v>
       </c>
       <c r="M56">
-        <v>1.66458726</v>
+        <v>1.69541295</v>
       </c>
       <c r="N56">
-        <v>3.70541274</v>
+        <v>3.67458705</v>
       </c>
       <c r="O56">
-        <v>0.8522449302</v>
+        <v>0.8451550214999999</v>
       </c>
       <c r="P56">
-        <v>2.8531678098</v>
+        <v>2.829432028499999</v>
       </c>
       <c r="Q56">
-        <v>3.4131678098</v>
+        <v>3.389432028499999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1182550721182514</v>
+        <v>0.1196706770389855</v>
       </c>
       <c r="T56">
-        <v>1.120856922195118</v>
+        <v>1.142755880102562</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.226024930648574</v>
+        <v>3.167369931909509</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08099815466754348</v>
+        <v>0.08094619616069133</v>
       </c>
       <c r="C57">
-        <v>23.22221886019915</v>
+        <v>22.77105228061382</v>
       </c>
       <c r="D57">
-        <v>45.92171886019915</v>
+        <v>45.95145228061383</v>
       </c>
       <c r="E57">
-        <v>24.95950000000001</v>
+        <v>25.44040000000001</v>
       </c>
       <c r="F57">
-        <v>26.4495</v>
+        <v>26.93040000000001</v>
       </c>
       <c r="G57">
         <v>3.75</v>
@@ -6089,28 +6089,28 @@
         <v>5.37</v>
       </c>
       <c r="M57">
-        <v>1.69541295</v>
+        <v>1.72623864</v>
       </c>
       <c r="N57">
-        <v>3.67458705</v>
+        <v>3.64376136</v>
       </c>
       <c r="O57">
-        <v>0.8451550214999999</v>
+        <v>0.8380651128</v>
       </c>
       <c r="P57">
-        <v>2.829432028499999</v>
+        <v>2.8056962472</v>
       </c>
       <c r="Q57">
-        <v>3.389432028499999</v>
+        <v>3.365696247199999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1196706770389855</v>
+        <v>0.1211506276379349</v>
       </c>
       <c r="T57">
-        <v>1.142755880102562</v>
+        <v>1.165650245187616</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.167369931909509</v>
+        <v>3.110809754553981</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08094619616069133</v>
+        <v>0.08089423765383918</v>
       </c>
       <c r="C58">
-        <v>22.77105228061382</v>
+        <v>22.31992422959863</v>
       </c>
       <c r="D58">
-        <v>45.95145228061383</v>
+        <v>45.98122422959864</v>
       </c>
       <c r="E58">
-        <v>25.44040000000001</v>
+        <v>25.92130000000001</v>
       </c>
       <c r="F58">
-        <v>26.93040000000001</v>
+        <v>27.4113</v>
       </c>
       <c r="G58">
         <v>3.75</v>
@@ -6171,28 +6171,28 @@
         <v>5.37</v>
       </c>
       <c r="M58">
-        <v>1.72623864</v>
+        <v>1.75706433</v>
       </c>
       <c r="N58">
-        <v>3.64376136</v>
+        <v>3.61293567</v>
       </c>
       <c r="O58">
-        <v>0.8380651128</v>
+        <v>0.8309752040999999</v>
       </c>
       <c r="P58">
-        <v>2.8056962472</v>
+        <v>2.7819604659</v>
       </c>
       <c r="Q58">
-        <v>3.365696247199999</v>
+        <v>3.341960465899999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1211506276379349</v>
+        <v>0.1226994131484632</v>
       </c>
       <c r="T58">
-        <v>1.165650245187616</v>
+        <v>1.189609464462672</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.110809754553981</v>
+        <v>3.056234144824964</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08089423765383918</v>
+        <v>0.08084227914698704</v>
       </c>
       <c r="C59">
-        <v>22.31992422959863</v>
+        <v>21.86883478209009</v>
       </c>
       <c r="D59">
-        <v>45.98122422959864</v>
+        <v>46.0110347820901</v>
       </c>
       <c r="E59">
-        <v>25.92130000000001</v>
+        <v>26.40220000000001</v>
       </c>
       <c r="F59">
-        <v>27.4113</v>
+        <v>27.89220000000001</v>
       </c>
       <c r="G59">
         <v>3.75</v>
@@ -6253,28 +6253,28 @@
         <v>5.37</v>
       </c>
       <c r="M59">
-        <v>1.75706433</v>
+        <v>1.787890020000001</v>
       </c>
       <c r="N59">
-        <v>3.61293567</v>
+        <v>3.582109979999999</v>
       </c>
       <c r="O59">
-        <v>0.8309752040999999</v>
+        <v>0.8238852953999999</v>
       </c>
       <c r="P59">
-        <v>2.7819604659</v>
+        <v>2.7582246846</v>
       </c>
       <c r="Q59">
-        <v>3.341960465899999</v>
+        <v>3.318224684599999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1226994131484632</v>
+        <v>0.1243219503499692</v>
       </c>
       <c r="T59">
-        <v>1.189609464462672</v>
+        <v>1.214709598941303</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.056234144824964</v>
+        <v>3.00354045267281</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08084227914698705</v>
+        <v>0.0843338606401349</v>
       </c>
       <c r="C60">
-        <v>21.86883478209009</v>
+        <v>19.46707002071998</v>
       </c>
       <c r="D60">
-        <v>46.01103478209009</v>
+        <v>44.09017002071998</v>
       </c>
       <c r="E60">
-        <v>26.4022</v>
+        <v>26.8831</v>
       </c>
       <c r="F60">
-        <v>27.8922</v>
+        <v>28.3731</v>
       </c>
       <c r="G60">
         <v>3.75</v>
@@ -6335,45 +6335,45 @@
         <v>5.37</v>
       </c>
       <c r="M60">
-        <v>1.78789002</v>
+        <v>2.04002589</v>
       </c>
       <c r="N60">
-        <v>3.58210998</v>
+        <v>3.32997411</v>
       </c>
       <c r="O60">
-        <v>0.8238852954000001</v>
+        <v>0.7658940452999999</v>
       </c>
       <c r="P60">
-        <v>2.7582246846</v>
+        <v>2.5640800647</v>
       </c>
       <c r="Q60">
-        <v>3.3182246846</v>
+        <v>3.124080064699999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1243219503499692</v>
+        <v>0.1260236357076461</v>
       </c>
       <c r="T60">
-        <v>1.214709598941303</v>
+        <v>1.24103413022377</v>
       </c>
       <c r="U60">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V60">
         <v>0.23</v>
       </c>
       <c r="W60">
-        <v>0.04935700000000001</v>
+        <v>0.055363</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.00354045267281</v>
+        <v>2.632319533944738</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0843338606401349</v>
+        <v>0.08434196213328274</v>
       </c>
       <c r="C61">
-        <v>19.46707002071998</v>
+        <v>18.9818995339422</v>
       </c>
       <c r="D61">
-        <v>44.09017002071998</v>
+        <v>44.0858995339422</v>
       </c>
       <c r="E61">
-        <v>26.8831</v>
+        <v>27.364</v>
       </c>
       <c r="F61">
-        <v>28.3731</v>
+        <v>28.854</v>
       </c>
       <c r="G61">
         <v>3.75</v>
@@ -6417,28 +6417,28 @@
         <v>5.37</v>
       </c>
       <c r="M61">
-        <v>2.04002589</v>
+        <v>2.0746026</v>
       </c>
       <c r="N61">
-        <v>3.32997411</v>
+        <v>3.2953974</v>
       </c>
       <c r="O61">
-        <v>0.7658940452999999</v>
+        <v>0.757941402</v>
       </c>
       <c r="P61">
-        <v>2.5640800647</v>
+        <v>2.537455998</v>
       </c>
       <c r="Q61">
-        <v>3.124080064699999</v>
+        <v>3.097455998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1260236357076461</v>
+        <v>0.1278104053332069</v>
       </c>
       <c r="T61">
-        <v>1.24103413022377</v>
+        <v>1.268674888070359</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.632319533944738</v>
+        <v>2.588447541712326</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08434196213328274</v>
+        <v>0.0843500636264306</v>
       </c>
       <c r="C62">
-        <v>18.9818995339422</v>
+        <v>18.49672987434611</v>
       </c>
       <c r="D62">
-        <v>44.0858995339422</v>
+        <v>44.08162987434611</v>
       </c>
       <c r="E62">
-        <v>27.364</v>
+        <v>27.8449</v>
       </c>
       <c r="F62">
-        <v>28.854</v>
+        <v>29.3349</v>
       </c>
       <c r="G62">
         <v>3.75</v>
@@ -6499,28 +6499,28 @@
         <v>5.37</v>
       </c>
       <c r="M62">
-        <v>2.0746026</v>
+        <v>2.10917931</v>
       </c>
       <c r="N62">
-        <v>3.2953974</v>
+        <v>3.26082069</v>
       </c>
       <c r="O62">
-        <v>0.757941402</v>
+        <v>0.7499887587</v>
       </c>
       <c r="P62">
-        <v>2.537455998</v>
+        <v>2.5108319313</v>
       </c>
       <c r="Q62">
-        <v>3.097455998</v>
+        <v>3.0708319313</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1278104053332069</v>
+        <v>0.1296888041703349</v>
       </c>
       <c r="T62">
-        <v>1.268674888070359</v>
+        <v>1.297733120678313</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.588447541712326</v>
+        <v>2.546013975454747</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0843500636264306</v>
+        <v>0.08435816511957846</v>
       </c>
       <c r="C63">
-        <v>18.49672987434611</v>
+        <v>18.01156104169142</v>
       </c>
       <c r="D63">
-        <v>44.08162987434611</v>
+        <v>44.07736104169143</v>
       </c>
       <c r="E63">
-        <v>27.8449</v>
+        <v>28.3258</v>
       </c>
       <c r="F63">
-        <v>29.3349</v>
+        <v>29.8158</v>
       </c>
       <c r="G63">
         <v>3.75</v>
@@ -6581,28 +6581,28 @@
         <v>5.37</v>
       </c>
       <c r="M63">
-        <v>2.10917931</v>
+        <v>2.143756020000001</v>
       </c>
       <c r="N63">
-        <v>3.26082069</v>
+        <v>3.22624398</v>
       </c>
       <c r="O63">
-        <v>0.7499887587</v>
+        <v>0.7420361153999999</v>
       </c>
       <c r="P63">
-        <v>2.5108319313</v>
+        <v>2.4842078646</v>
       </c>
       <c r="Q63">
-        <v>3.0708319313</v>
+        <v>3.044207864599999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1296888041703349</v>
+        <v>0.1316660661041538</v>
       </c>
       <c r="T63">
-        <v>1.297733120678313</v>
+        <v>1.328320733949843</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.546013975454747</v>
+        <v>2.504949233915154</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08435816511957846</v>
+        <v>0.08625815661272632</v>
       </c>
       <c r="C64">
-        <v>18.01156104169142</v>
+        <v>16.55184587233813</v>
       </c>
       <c r="D64">
-        <v>44.07736104169143</v>
+        <v>43.09854587233814</v>
       </c>
       <c r="E64">
-        <v>28.3258</v>
+        <v>28.8067</v>
       </c>
       <c r="F64">
-        <v>29.8158</v>
+        <v>30.2967</v>
       </c>
       <c r="G64">
         <v>3.75</v>
@@ -6663,45 +6663,45 @@
         <v>5.37</v>
       </c>
       <c r="M64">
-        <v>2.143756020000001</v>
+        <v>2.29648986</v>
       </c>
       <c r="N64">
-        <v>3.22624398</v>
+        <v>3.07351014</v>
       </c>
       <c r="O64">
-        <v>0.7420361153999999</v>
+        <v>0.7069073322</v>
       </c>
       <c r="P64">
-        <v>2.4842078646</v>
+        <v>2.3666028078</v>
       </c>
       <c r="Q64">
-        <v>3.044207864599999</v>
+        <v>2.926602807799999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1316660661041538</v>
+        <v>0.1337502070614225</v>
       </c>
       <c r="T64">
-        <v>1.328320733949843</v>
+        <v>1.360561731722536</v>
       </c>
       <c r="U64">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V64">
         <v>0.23</v>
       </c>
       <c r="W64">
-        <v>0.055363</v>
+        <v>0.05836600000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.504949233915154</v>
+        <v>2.338351278415834</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08625815661272632</v>
+        <v>0.08629628810587417</v>
       </c>
       <c r="C65">
-        <v>16.55184587233813</v>
+        <v>16.05174652929724</v>
       </c>
       <c r="D65">
-        <v>43.09854587233814</v>
+        <v>43.07934652929724</v>
       </c>
       <c r="E65">
-        <v>28.8067</v>
+        <v>29.2876</v>
       </c>
       <c r="F65">
-        <v>30.2967</v>
+        <v>30.7776</v>
       </c>
       <c r="G65">
         <v>3.75</v>
@@ -6745,28 +6745,28 @@
         <v>5.37</v>
       </c>
       <c r="M65">
-        <v>2.29648986</v>
+        <v>2.33294208</v>
       </c>
       <c r="N65">
-        <v>3.07351014</v>
+        <v>3.03705792</v>
       </c>
       <c r="O65">
-        <v>0.7069073322</v>
+        <v>0.6985233216</v>
       </c>
       <c r="P65">
-        <v>2.3666028078</v>
+        <v>2.3385345984</v>
       </c>
       <c r="Q65">
-        <v>2.926602807799999</v>
+        <v>2.898534598399999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1337502070614225</v>
+        <v>0.1359501336274282</v>
       </c>
       <c r="T65">
-        <v>1.360561731722536</v>
+        <v>1.394593896038157</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.338351278415834</v>
+        <v>2.301814539690586</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08629628810587417</v>
+        <v>0.08633441959902202</v>
       </c>
       <c r="C66">
-        <v>16.05174652929724</v>
+        <v>15.55166428431058</v>
       </c>
       <c r="D66">
-        <v>43.07934652929724</v>
+        <v>43.06016428431059</v>
       </c>
       <c r="E66">
-        <v>29.2876</v>
+        <v>29.76850000000001</v>
       </c>
       <c r="F66">
-        <v>30.7776</v>
+        <v>31.25850000000001</v>
       </c>
       <c r="G66">
         <v>3.75</v>
@@ -6827,28 +6827,28 @@
         <v>5.37</v>
       </c>
       <c r="M66">
-        <v>2.33294208</v>
+        <v>2.369394300000001</v>
       </c>
       <c r="N66">
-        <v>3.03705792</v>
+        <v>3.000605699999999</v>
       </c>
       <c r="O66">
-        <v>0.6985233216</v>
+        <v>0.6901393109999999</v>
       </c>
       <c r="P66">
-        <v>2.3385345984</v>
+        <v>2.310466389</v>
       </c>
       <c r="Q66">
-        <v>2.898534598399999</v>
+        <v>2.870466388999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1359501336274282</v>
+        <v>0.13827577028292</v>
       </c>
       <c r="T66">
-        <v>1.394593896038157</v>
+        <v>1.430570755457528</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.301814539690586</v>
+        <v>2.266402008310731</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08633441959902202</v>
+        <v>0.08637255109216987</v>
       </c>
       <c r="C67">
-        <v>15.55166428431058</v>
+        <v>15.05159911454822</v>
       </c>
       <c r="D67">
-        <v>43.06016428431059</v>
+        <v>43.04099911454823</v>
       </c>
       <c r="E67">
-        <v>29.76850000000001</v>
+        <v>30.2494</v>
       </c>
       <c r="F67">
-        <v>31.25850000000001</v>
+        <v>31.7394</v>
       </c>
       <c r="G67">
         <v>3.75</v>
@@ -6909,28 +6909,28 @@
         <v>5.37</v>
       </c>
       <c r="M67">
-        <v>2.369394300000001</v>
+        <v>2.40584652</v>
       </c>
       <c r="N67">
-        <v>3.000605699999999</v>
+        <v>2.96415348</v>
       </c>
       <c r="O67">
-        <v>0.6901393109999999</v>
+        <v>0.6817553004</v>
       </c>
       <c r="P67">
-        <v>2.310466389</v>
+        <v>2.2823981796</v>
       </c>
       <c r="Q67">
-        <v>2.870466388999999</v>
+        <v>2.8423981796</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.13827577028292</v>
+        <v>0.1407382090946173</v>
       </c>
       <c r="T67">
-        <v>1.430570755457528</v>
+        <v>1.468663900725098</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.266402008310731</v>
+        <v>2.232062583942387</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08637255109216987</v>
+        <v>0.08641068258531773</v>
       </c>
       <c r="C68">
-        <v>15.05159911454822</v>
+        <v>14.55155099722084</v>
       </c>
       <c r="D68">
-        <v>43.04099911454823</v>
+        <v>43.02185099722084</v>
       </c>
       <c r="E68">
-        <v>30.2494</v>
+        <v>30.7303</v>
       </c>
       <c r="F68">
-        <v>31.7394</v>
+        <v>32.2203</v>
       </c>
       <c r="G68">
         <v>3.75</v>
@@ -6991,28 +6991,28 @@
         <v>5.37</v>
       </c>
       <c r="M68">
-        <v>2.40584652</v>
+        <v>2.44229874</v>
       </c>
       <c r="N68">
-        <v>2.96415348</v>
+        <v>2.92770126</v>
       </c>
       <c r="O68">
-        <v>0.6817553004</v>
+        <v>0.6733712897999999</v>
       </c>
       <c r="P68">
-        <v>2.2823981796</v>
+        <v>2.2543299702</v>
       </c>
       <c r="Q68">
-        <v>2.8423981796</v>
+        <v>2.814329970199999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1407382090946173</v>
+        <v>0.1433498866221749</v>
       </c>
       <c r="T68">
-        <v>1.468663900725098</v>
+        <v>1.509065721463428</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.232062583942387</v>
+        <v>2.198748217017874</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08641068258531773</v>
+        <v>0.08644881407846558</v>
       </c>
       <c r="C69">
-        <v>14.55155099722084</v>
+        <v>14.05151990957962</v>
       </c>
       <c r="D69">
-        <v>43.02185099722084</v>
+        <v>43.00271990957962</v>
       </c>
       <c r="E69">
-        <v>30.7303</v>
+        <v>31.21120000000001</v>
       </c>
       <c r="F69">
-        <v>32.2203</v>
+        <v>32.70120000000001</v>
       </c>
       <c r="G69">
         <v>3.75</v>
@@ -7073,28 +7073,28 @@
         <v>5.37</v>
       </c>
       <c r="M69">
-        <v>2.44229874</v>
+        <v>2.478750960000001</v>
       </c>
       <c r="N69">
-        <v>2.92770126</v>
+        <v>2.891249039999999</v>
       </c>
       <c r="O69">
-        <v>0.6733712897999999</v>
+        <v>0.6649872791999999</v>
       </c>
       <c r="P69">
-        <v>2.2543299702</v>
+        <v>2.226261760799999</v>
       </c>
       <c r="Q69">
-        <v>2.814329970199999</v>
+        <v>2.786261760799999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1433498866221749</v>
+        <v>0.1461247939952049</v>
       </c>
       <c r="T69">
-        <v>1.509065721463428</v>
+        <v>1.551992655997905</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.198748217017874</v>
+        <v>2.166413684414669</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08644881407846558</v>
+        <v>0.08648694557161343</v>
       </c>
       <c r="C70">
-        <v>14.05151990957962</v>
+        <v>13.55150582891626</v>
       </c>
       <c r="D70">
-        <v>43.00271990957962</v>
+        <v>42.98360582891626</v>
       </c>
       <c r="E70">
-        <v>31.21120000000001</v>
+        <v>31.69210000000001</v>
       </c>
       <c r="F70">
-        <v>32.70120000000001</v>
+        <v>33.18210000000001</v>
       </c>
       <c r="G70">
         <v>3.75</v>
@@ -7155,28 +7155,28 @@
         <v>5.37</v>
       </c>
       <c r="M70">
-        <v>2.478750960000001</v>
+        <v>2.515203180000001</v>
       </c>
       <c r="N70">
-        <v>2.891249039999999</v>
+        <v>2.854796819999999</v>
       </c>
       <c r="O70">
-        <v>0.6649872791999999</v>
+        <v>0.6566032685999998</v>
       </c>
       <c r="P70">
-        <v>2.226261760799999</v>
+        <v>2.198193551399999</v>
       </c>
       <c r="Q70">
-        <v>2.786261760799999</v>
+        <v>2.758193551399999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1461247939952049</v>
+        <v>0.1490787276503659</v>
       </c>
       <c r="T70">
-        <v>1.551992655997905</v>
+        <v>1.597689070179768</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.166413684414669</v>
+        <v>2.135016384640544</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08648694557161343</v>
+        <v>0.08652507706476129</v>
       </c>
       <c r="C71">
-        <v>13.55150582891626</v>
+        <v>13.05150873256276</v>
       </c>
       <c r="D71">
-        <v>42.98360582891626</v>
+        <v>42.96450873256276</v>
       </c>
       <c r="E71">
-        <v>31.69210000000001</v>
+        <v>32.173</v>
       </c>
       <c r="F71">
-        <v>33.18210000000001</v>
+        <v>33.663</v>
       </c>
       <c r="G71">
         <v>3.75</v>
@@ -7237,28 +7237,28 @@
         <v>5.37</v>
       </c>
       <c r="M71">
-        <v>2.515203180000001</v>
+        <v>2.5516554</v>
       </c>
       <c r="N71">
-        <v>2.854796819999999</v>
+        <v>2.8183446</v>
       </c>
       <c r="O71">
-        <v>0.6566032685999998</v>
+        <v>0.6482192579999999</v>
       </c>
       <c r="P71">
-        <v>2.198193551399999</v>
+        <v>2.170125342</v>
       </c>
       <c r="Q71">
-        <v>2.758193551399999</v>
+        <v>2.730125341999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1490787276503659</v>
+        <v>0.152229590215871</v>
       </c>
       <c r="T71">
-        <v>1.597689070179768</v>
+        <v>1.646431911973754</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.135016384640544</v>
+        <v>2.10451615057425</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08652507706476129</v>
+        <v>0.08656320855790914</v>
       </c>
       <c r="C72">
-        <v>13.05150873256276</v>
+        <v>12.55152859789138</v>
       </c>
       <c r="D72">
-        <v>42.96450873256276</v>
+        <v>42.94542859789139</v>
       </c>
       <c r="E72">
-        <v>32.173</v>
+        <v>32.65390000000001</v>
       </c>
       <c r="F72">
-        <v>33.663</v>
+        <v>34.14390000000001</v>
       </c>
       <c r="G72">
         <v>3.75</v>
@@ -7319,28 +7319,28 @@
         <v>5.37</v>
       </c>
       <c r="M72">
-        <v>2.5516554</v>
+        <v>2.588107620000001</v>
       </c>
       <c r="N72">
-        <v>2.8183446</v>
+        <v>2.781892379999999</v>
       </c>
       <c r="O72">
-        <v>0.6482192579999999</v>
+        <v>0.6398352473999999</v>
       </c>
       <c r="P72">
-        <v>2.170125342</v>
+        <v>2.142057132599999</v>
       </c>
       <c r="Q72">
-        <v>2.730125341999999</v>
+        <v>2.702057132599999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.152229590215871</v>
+        <v>0.1555977536479626</v>
       </c>
       <c r="T72">
-        <v>1.646431911973754</v>
+        <v>1.698536329063877</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.10451615057425</v>
+        <v>2.074875078030951</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08656320855790914</v>
+        <v>0.08660134005105699</v>
       </c>
       <c r="C73">
-        <v>12.55152859789139</v>
+        <v>12.05156540231464</v>
       </c>
       <c r="D73">
-        <v>42.94542859789139</v>
+        <v>42.92636540231464</v>
       </c>
       <c r="E73">
-        <v>32.6539</v>
+        <v>33.1348</v>
       </c>
       <c r="F73">
-        <v>34.1439</v>
+        <v>34.6248</v>
       </c>
       <c r="G73">
         <v>3.75</v>
@@ -7401,28 +7401,28 @@
         <v>5.37</v>
       </c>
       <c r="M73">
-        <v>2.58810762</v>
+        <v>2.62455984</v>
       </c>
       <c r="N73">
-        <v>2.78189238</v>
+        <v>2.74544016</v>
       </c>
       <c r="O73">
-        <v>0.6398352474</v>
+        <v>0.6314512367999999</v>
       </c>
       <c r="P73">
-        <v>2.1420571326</v>
+        <v>2.1139889232</v>
       </c>
       <c r="Q73">
-        <v>2.702057132599999</v>
+        <v>2.6739889232</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1555977536479626</v>
+        <v>0.1592065001823464</v>
       </c>
       <c r="T73">
-        <v>1.698536329063877</v>
+        <v>1.754362490231866</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.074875078030951</v>
+        <v>2.046057368613855</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08660134005105699</v>
+        <v>0.08663947154420486</v>
       </c>
       <c r="C74">
-        <v>12.05156540231464</v>
+        <v>11.55161912328502</v>
       </c>
       <c r="D74">
-        <v>42.92636540231464</v>
+        <v>42.90731912328502</v>
       </c>
       <c r="E74">
-        <v>33.1348</v>
+        <v>33.6157</v>
       </c>
       <c r="F74">
-        <v>34.6248</v>
+        <v>35.1057</v>
       </c>
       <c r="G74">
         <v>3.75</v>
@@ -7483,28 +7483,28 @@
         <v>5.37</v>
       </c>
       <c r="M74">
-        <v>2.62455984</v>
+        <v>2.66101206</v>
       </c>
       <c r="N74">
-        <v>2.74544016</v>
+        <v>2.70898794</v>
       </c>
       <c r="O74">
-        <v>0.6314512367999999</v>
+        <v>0.6230672262000001</v>
       </c>
       <c r="P74">
-        <v>2.1139889232</v>
+        <v>2.0859207138</v>
       </c>
       <c r="Q74">
-        <v>2.6739889232</v>
+        <v>2.6459207138</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1592065001823464</v>
+        <v>0.1630825612748328</v>
       </c>
       <c r="T74">
-        <v>1.754362490231866</v>
+        <v>1.814323922597484</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.046057368613855</v>
+        <v>2.018029185482158</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08663947154420486</v>
+        <v>0.0947687630373527</v>
       </c>
       <c r="C75">
-        <v>11.55161912328502</v>
+        <v>7.362768207539709</v>
       </c>
       <c r="D75">
-        <v>42.90731912328502</v>
+        <v>39.19936820753971</v>
       </c>
       <c r="E75">
-        <v>33.6157</v>
+        <v>34.0966</v>
       </c>
       <c r="F75">
-        <v>35.1057</v>
+        <v>35.5866</v>
       </c>
       <c r="G75">
         <v>3.75</v>
@@ -7565,45 +7565,45 @@
         <v>5.37</v>
       </c>
       <c r="M75">
-        <v>2.66101206</v>
+        <v>3.202794</v>
       </c>
       <c r="N75">
-        <v>2.70898794</v>
+        <v>2.167206</v>
       </c>
       <c r="O75">
-        <v>0.6230672262000001</v>
+        <v>0.4984573799999999</v>
       </c>
       <c r="P75">
-        <v>2.0859207138</v>
+        <v>1.66874862</v>
       </c>
       <c r="Q75">
-        <v>2.6459207138</v>
+        <v>2.228748619999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1630825612748328</v>
+        <v>0.167256780912895</v>
       </c>
       <c r="T75">
-        <v>1.814323922597484</v>
+        <v>1.87889777283738</v>
       </c>
       <c r="U75">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V75">
         <v>0.23</v>
       </c>
       <c r="W75">
-        <v>0.05836600000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y75">
-        <v>2.018029185482158</v>
+        <v>1.676661065307353</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0947687630373527</v>
+        <v>0.09491623453050055</v>
       </c>
       <c r="C76">
-        <v>7.362768207539709</v>
+        <v>6.820512249457941</v>
       </c>
       <c r="D76">
-        <v>39.19936820753971</v>
+        <v>39.13801224945794</v>
       </c>
       <c r="E76">
-        <v>34.0966</v>
+        <v>34.5775</v>
       </c>
       <c r="F76">
-        <v>35.5866</v>
+        <v>36.0675</v>
       </c>
       <c r="G76">
         <v>3.75</v>
@@ -7647,28 +7647,28 @@
         <v>5.37</v>
       </c>
       <c r="M76">
-        <v>3.202794</v>
+        <v>3.246075</v>
       </c>
       <c r="N76">
-        <v>2.167206</v>
+        <v>2.123925</v>
       </c>
       <c r="O76">
-        <v>0.4984573799999999</v>
+        <v>0.48850275</v>
       </c>
       <c r="P76">
-        <v>1.66874862</v>
+        <v>1.63542225</v>
       </c>
       <c r="Q76">
-        <v>2.228748619999999</v>
+        <v>2.19542225</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.167256780912895</v>
+        <v>0.1717649381220022</v>
       </c>
       <c r="T76">
-        <v>1.87889777283738</v>
+        <v>1.948637531096469</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.676661065307353</v>
+        <v>1.654305584436589</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09491623453050055</v>
+        <v>0.0950637060236484</v>
       </c>
       <c r="C77">
-        <v>6.820512249457941</v>
+        <v>6.278448063365708</v>
       </c>
       <c r="D77">
-        <v>39.13801224945794</v>
+        <v>39.07684806336571</v>
       </c>
       <c r="E77">
-        <v>34.5775</v>
+        <v>35.0584</v>
       </c>
       <c r="F77">
-        <v>36.0675</v>
+        <v>36.5484</v>
       </c>
       <c r="G77">
         <v>3.75</v>
@@ -7729,28 +7729,28 @@
         <v>5.37</v>
       </c>
       <c r="M77">
-        <v>3.246075</v>
+        <v>3.289356</v>
       </c>
       <c r="N77">
-        <v>2.123925</v>
+        <v>2.080644</v>
       </c>
       <c r="O77">
-        <v>0.48850275</v>
+        <v>0.47854812</v>
       </c>
       <c r="P77">
-        <v>1.63542225</v>
+        <v>1.60209588</v>
       </c>
       <c r="Q77">
-        <v>2.19542225</v>
+        <v>2.162095879999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1717649381220022</v>
+        <v>0.176648775098535</v>
       </c>
       <c r="T77">
-        <v>1.948637531096469</v>
+        <v>2.024188935877147</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.654305584436589</v>
+        <v>1.632538405694002</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0950637060236484</v>
+        <v>0.09521117751679625</v>
       </c>
       <c r="C78">
-        <v>6.278448063365708</v>
+        <v>5.736574751572405</v>
       </c>
       <c r="D78">
-        <v>39.07684806336571</v>
+        <v>39.01587475157241</v>
       </c>
       <c r="E78">
-        <v>35.0584</v>
+        <v>35.5393</v>
       </c>
       <c r="F78">
-        <v>36.5484</v>
+        <v>37.02930000000001</v>
       </c>
       <c r="G78">
         <v>3.75</v>
@@ -7811,28 +7811,28 @@
         <v>5.37</v>
       </c>
       <c r="M78">
-        <v>3.289356</v>
+        <v>3.332637000000001</v>
       </c>
       <c r="N78">
-        <v>2.080644</v>
+        <v>2.037363</v>
       </c>
       <c r="O78">
-        <v>0.47854812</v>
+        <v>0.4685934899999999</v>
       </c>
       <c r="P78">
-        <v>1.60209588</v>
+        <v>1.56876951</v>
       </c>
       <c r="Q78">
-        <v>2.162095879999999</v>
+        <v>2.128769509999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.176648775098535</v>
+        <v>0.1819572935512881</v>
       </c>
       <c r="T78">
-        <v>2.024188935877147</v>
+        <v>2.106310028030059</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.632538405694002</v>
+        <v>1.611336608217457</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09521117751679625</v>
+        <v>0.09535864900994412</v>
       </c>
       <c r="C79">
-        <v>5.736574751572405</v>
+        <v>5.194891421981502</v>
       </c>
       <c r="D79">
-        <v>39.01587475157241</v>
+        <v>38.95509142198151</v>
       </c>
       <c r="E79">
-        <v>35.5393</v>
+        <v>36.0202</v>
       </c>
       <c r="F79">
-        <v>37.02930000000001</v>
+        <v>37.5102</v>
       </c>
       <c r="G79">
         <v>3.75</v>
@@ -7893,28 +7893,28 @@
         <v>5.37</v>
       </c>
       <c r="M79">
-        <v>3.332637000000001</v>
+        <v>3.375918</v>
       </c>
       <c r="N79">
-        <v>2.037363</v>
+        <v>1.994082</v>
       </c>
       <c r="O79">
-        <v>0.4685934899999999</v>
+        <v>0.4586388599999999</v>
       </c>
       <c r="P79">
-        <v>1.56876951</v>
+        <v>1.53544314</v>
       </c>
       <c r="Q79">
-        <v>2.128769509999999</v>
+        <v>2.09544314</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1819572935512881</v>
+        <v>0.1877484045906551</v>
       </c>
       <c r="T79">
-        <v>2.106310028030059</v>
+        <v>2.195896674015054</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.611336608217457</v>
+        <v>1.590678446573643</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09535864900994412</v>
+        <v>0.09550612050309196</v>
       </c>
       <c r="C80">
-        <v>5.194891421981502</v>
+        <v>4.653397188047073</v>
       </c>
       <c r="D80">
-        <v>38.95509142198151</v>
+        <v>38.89449718804708</v>
       </c>
       <c r="E80">
-        <v>36.0202</v>
+        <v>36.5011</v>
       </c>
       <c r="F80">
-        <v>37.5102</v>
+        <v>37.9911</v>
       </c>
       <c r="G80">
         <v>3.75</v>
@@ -7975,28 +7975,28 @@
         <v>5.37</v>
       </c>
       <c r="M80">
-        <v>3.375918</v>
+        <v>3.419199</v>
       </c>
       <c r="N80">
-        <v>1.994082</v>
+        <v>1.950801</v>
       </c>
       <c r="O80">
-        <v>0.4586388599999999</v>
+        <v>0.44868423</v>
       </c>
       <c r="P80">
-        <v>1.53544314</v>
+        <v>1.50211677</v>
       </c>
       <c r="Q80">
-        <v>2.09544314</v>
+        <v>2.062116769999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1877484045906551</v>
+        <v>0.1940910500147237</v>
       </c>
       <c r="T80">
-        <v>2.195896674015054</v>
+        <v>2.294015381522429</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.590678446573643</v>
+        <v>1.57054327636385</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09550612050309196</v>
+        <v>0.09565359199623982</v>
       </c>
       <c r="C81">
-        <v>4.653397188047073</v>
+        <v>4.112091168730643</v>
       </c>
       <c r="D81">
-        <v>38.89449718804708</v>
+        <v>38.83409116873065</v>
       </c>
       <c r="E81">
-        <v>36.5011</v>
+        <v>36.98200000000001</v>
       </c>
       <c r="F81">
-        <v>37.9911</v>
+        <v>38.47200000000001</v>
       </c>
       <c r="G81">
         <v>3.75</v>
@@ -8057,28 +8057,28 @@
         <v>5.37</v>
       </c>
       <c r="M81">
-        <v>3.419199</v>
+        <v>3.462480000000001</v>
       </c>
       <c r="N81">
-        <v>1.950801</v>
+        <v>1.907519999999999</v>
       </c>
       <c r="O81">
-        <v>0.44868423</v>
+        <v>0.4387295999999999</v>
       </c>
       <c r="P81">
-        <v>1.50211677</v>
+        <v>1.4687904</v>
       </c>
       <c r="Q81">
-        <v>2.062116769999999</v>
+        <v>2.028790399999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1940910500147237</v>
+        <v>0.2010679599811991</v>
       </c>
       <c r="T81">
-        <v>2.294015381522429</v>
+        <v>2.401945959780542</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.57054327636385</v>
+        <v>1.550911485409302</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09565359199623982</v>
+        <v>0.09580106348938766</v>
       </c>
       <c r="C82">
-        <v>4.112091168730643</v>
+        <v>3.570972488458573</v>
       </c>
       <c r="D82">
-        <v>38.83409116873065</v>
+        <v>38.77387248845858</v>
       </c>
       <c r="E82">
-        <v>36.98200000000001</v>
+        <v>37.4629</v>
       </c>
       <c r="F82">
-        <v>38.47200000000001</v>
+        <v>38.95290000000001</v>
       </c>
       <c r="G82">
         <v>3.75</v>
@@ -8139,28 +8139,28 @@
         <v>5.37</v>
       </c>
       <c r="M82">
-        <v>3.462480000000001</v>
+        <v>3.505761000000001</v>
       </c>
       <c r="N82">
-        <v>1.907519999999999</v>
+        <v>1.864239</v>
       </c>
       <c r="O82">
-        <v>0.4387295999999999</v>
+        <v>0.4287749699999999</v>
       </c>
       <c r="P82">
-        <v>1.4687904</v>
+        <v>1.43546403</v>
       </c>
       <c r="Q82">
-        <v>2.028790399999999</v>
+        <v>1.995464029999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2010679599811991</v>
+        <v>0.2087792815230931</v>
       </c>
       <c r="T82">
-        <v>2.401945959780542</v>
+        <v>2.521237651539509</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.550911485409302</v>
+        <v>1.531764430033878</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09580106348938766</v>
+        <v>0.09594853498253553</v>
       </c>
       <c r="C83">
-        <v>3.570972488458573</v>
+        <v>3.030040277079642</v>
       </c>
       <c r="D83">
-        <v>38.77387248845858</v>
+        <v>38.71384027707965</v>
       </c>
       <c r="E83">
-        <v>37.4629</v>
+        <v>37.9438</v>
       </c>
       <c r="F83">
-        <v>38.95290000000001</v>
+        <v>39.43380000000001</v>
       </c>
       <c r="G83">
         <v>3.75</v>
@@ -8221,28 +8221,28 @@
         <v>5.37</v>
       </c>
       <c r="M83">
-        <v>3.505761000000001</v>
+        <v>3.549042</v>
       </c>
       <c r="N83">
-        <v>1.864239</v>
+        <v>1.820958</v>
       </c>
       <c r="O83">
-        <v>0.4287749699999999</v>
+        <v>0.41882034</v>
       </c>
       <c r="P83">
-        <v>1.43546403</v>
+        <v>1.40213766</v>
       </c>
       <c r="Q83">
-        <v>1.995464029999999</v>
+        <v>1.962137659999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2087792815230931</v>
+        <v>0.2173474165696418</v>
       </c>
       <c r="T83">
-        <v>2.521237651539509</v>
+        <v>2.653783975716138</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.531764430033878</v>
+        <v>1.513084376009075</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09594853498253553</v>
+        <v>0.1353447908844559</v>
       </c>
       <c r="C84">
-        <v>3.030040277079642</v>
+        <v>-8.778211474772167</v>
       </c>
       <c r="D84">
-        <v>38.71384027707965</v>
+        <v>27.38648852522784</v>
       </c>
       <c r="E84">
-        <v>37.9438</v>
+        <v>38.4247</v>
       </c>
       <c r="F84">
-        <v>39.43380000000001</v>
+        <v>39.9147</v>
       </c>
       <c r="G84">
         <v>3.75</v>
@@ -8303,45 +8303,45 @@
         <v>5.37</v>
       </c>
       <c r="M84">
-        <v>3.549042</v>
+        <v>5.859477960000001</v>
       </c>
       <c r="N84">
-        <v>1.820958</v>
+        <v>-0.4894779600000012</v>
       </c>
       <c r="O84">
-        <v>0.41882034</v>
+        <v>-0.1125799308000003</v>
       </c>
       <c r="P84">
-        <v>1.40213766</v>
+        <v>-0.3768980292000009</v>
       </c>
       <c r="Q84">
-        <v>1.962137659999999</v>
+        <v>0.1831019707999987</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2173474165696418</v>
+        <v>0.2304934416637292</v>
       </c>
       <c r="T84">
-        <v>2.653783975716138</v>
+        <v>2.857148802984689</v>
       </c>
       <c r="U84">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.23</v>
+        <v>0.2107866960899021</v>
       </c>
       <c r="W84">
-        <v>0.0693</v>
+        <v>0.1158565130140024</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>1.513084376009075</v>
+        <v>0.9164638960430528</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1353447908844559</v>
+        <v>0.136354790884456</v>
       </c>
       <c r="C85">
-        <v>-8.778211474772167</v>
+        <v>-9.463012473112105</v>
       </c>
       <c r="D85">
-        <v>27.38648852522784</v>
+        <v>27.1825875268879</v>
       </c>
       <c r="E85">
-        <v>38.4247</v>
+        <v>38.90560000000001</v>
       </c>
       <c r="F85">
-        <v>39.9147</v>
+        <v>40.39560000000001</v>
       </c>
       <c r="G85">
         <v>3.75</v>
@@ -8385,37 +8385,37 @@
         <v>5.37</v>
       </c>
       <c r="M85">
-        <v>5.859477960000001</v>
+        <v>5.930074080000002</v>
       </c>
       <c r="N85">
-        <v>-0.4894779600000012</v>
+        <v>-0.5600740800000015</v>
       </c>
       <c r="O85">
-        <v>-0.1125799308000003</v>
+        <v>-0.1288170384000003</v>
       </c>
       <c r="P85">
-        <v>-0.3768980292000009</v>
+        <v>-0.4312570416000011</v>
       </c>
       <c r="Q85">
-        <v>0.1831019707999987</v>
+        <v>0.1287429583999985</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2304934416637292</v>
+        <v>0.2420367817677123</v>
       </c>
       <c r="T85">
-        <v>2.857148802984689</v>
+        <v>3.035720603171232</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2107866960899021</v>
+        <v>0.2082773306602604</v>
       </c>
       <c r="W85">
-        <v>0.1158565130140024</v>
+        <v>0.1162248878590738</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9164638960430528</v>
+        <v>0.9055536115663497</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1363547908844559</v>
+        <v>0.1373647908844559</v>
       </c>
       <c r="C86">
-        <v>-9.463012473112091</v>
+        <v>-10.14479969615982</v>
       </c>
       <c r="D86">
-        <v>27.18258752688791</v>
+        <v>26.98170030384018</v>
       </c>
       <c r="E86">
-        <v>38.9056</v>
+        <v>39.3865</v>
       </c>
       <c r="F86">
-        <v>40.3956</v>
+        <v>40.8765</v>
       </c>
       <c r="G86">
         <v>3.75</v>
@@ -8467,37 +8467,37 @@
         <v>5.37</v>
       </c>
       <c r="M86">
-        <v>5.930074080000001</v>
+        <v>6.000670200000001</v>
       </c>
       <c r="N86">
-        <v>-0.5600740800000006</v>
+        <v>-0.6306702000000008</v>
       </c>
       <c r="O86">
-        <v>-0.1288170384000001</v>
+        <v>-0.1450541460000002</v>
       </c>
       <c r="P86">
-        <v>-0.4312570416000004</v>
+        <v>-0.4856160540000006</v>
       </c>
       <c r="Q86">
-        <v>0.1287429583999992</v>
+        <v>0.07438394599999898</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2420367817677122</v>
+        <v>0.2551192338855596</v>
       </c>
       <c r="T86">
-        <v>3.03572060317123</v>
+        <v>3.238101976715979</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2082773306602605</v>
+        <v>0.2058270091230809</v>
       </c>
       <c r="W86">
-        <v>0.1162248878590738</v>
+        <v>0.1165845950607317</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9055536115663498</v>
+        <v>0.8949000396655692</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1373647908844559</v>
+        <v>0.1383747908844559</v>
       </c>
       <c r="C87">
-        <v>-10.14479969615982</v>
+        <v>-10.82363947175962</v>
       </c>
       <c r="D87">
-        <v>26.98170030384018</v>
+        <v>26.78376052824039</v>
       </c>
       <c r="E87">
-        <v>39.3865</v>
+        <v>39.8674</v>
       </c>
       <c r="F87">
-        <v>40.8765</v>
+        <v>41.35740000000001</v>
       </c>
       <c r="G87">
         <v>3.75</v>
@@ -8549,37 +8549,37 @@
         <v>5.37</v>
       </c>
       <c r="M87">
-        <v>6.000670200000001</v>
+        <v>6.071266320000001</v>
       </c>
       <c r="N87">
-        <v>-0.6306702000000008</v>
+        <v>-0.7012663200000011</v>
       </c>
       <c r="O87">
-        <v>-0.1450541460000002</v>
+        <v>-0.1612912536000003</v>
       </c>
       <c r="P87">
-        <v>-0.4856160540000006</v>
+        <v>-0.5399750664000008</v>
       </c>
       <c r="Q87">
-        <v>0.07438394599999898</v>
+        <v>0.0200249335999988</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2551192338855596</v>
+        <v>0.2700706077345282</v>
       </c>
       <c r="T87">
-        <v>3.238101976715979</v>
+        <v>3.469394975052834</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2058270091230809</v>
+        <v>0.2034336718076963</v>
       </c>
       <c r="W87">
-        <v>0.1165845950607317</v>
+        <v>0.1169359369786302</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8949000396655692</v>
+        <v>0.8844942252508533</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1383747908844559</v>
+        <v>0.1393847908844559</v>
       </c>
       <c r="C88">
-        <v>-10.82363947175962</v>
+        <v>-11.49959619558609</v>
       </c>
       <c r="D88">
-        <v>26.78376052824039</v>
+        <v>26.58870380441391</v>
       </c>
       <c r="E88">
-        <v>39.8674</v>
+        <v>40.3483</v>
       </c>
       <c r="F88">
-        <v>41.35740000000001</v>
+        <v>41.8383</v>
       </c>
       <c r="G88">
         <v>3.75</v>
@@ -8631,37 +8631,37 @@
         <v>5.37</v>
       </c>
       <c r="M88">
-        <v>6.071266320000001</v>
+        <v>6.141862440000001</v>
       </c>
       <c r="N88">
-        <v>-0.7012663200000011</v>
+        <v>-0.7718624400000014</v>
       </c>
       <c r="O88">
-        <v>-0.1612912536000003</v>
+        <v>-0.1775283612000003</v>
       </c>
       <c r="P88">
-        <v>-0.5399750664000008</v>
+        <v>-0.5943340788000011</v>
       </c>
       <c r="Q88">
-        <v>0.0200249335999988</v>
+        <v>-0.0343340788000015</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2700706077345282</v>
+        <v>0.2873221929448765</v>
       </c>
       <c r="T88">
-        <v>3.469394975052834</v>
+        <v>3.73627151159536</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2034336718076963</v>
+        <v>0.2010953537409411</v>
       </c>
       <c r="W88">
-        <v>0.1169359369786302</v>
+        <v>0.1172792020708299</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8844942252508533</v>
+        <v>0.8743276249606136</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1393847908844559</v>
+        <v>0.1403947908844559</v>
       </c>
       <c r="C89">
-        <v>-11.49959619558609</v>
+        <v>-12.17273240099217</v>
       </c>
       <c r="D89">
-        <v>26.58870380441391</v>
+        <v>26.39646759900783</v>
       </c>
       <c r="E89">
-        <v>40.3483</v>
+        <v>40.8292</v>
       </c>
       <c r="F89">
-        <v>41.8383</v>
+        <v>42.3192</v>
       </c>
       <c r="G89">
         <v>3.75</v>
@@ -8713,37 +8713,37 @@
         <v>5.37</v>
       </c>
       <c r="M89">
-        <v>6.141862440000001</v>
+        <v>6.212458560000001</v>
       </c>
       <c r="N89">
-        <v>-0.7718624400000014</v>
+        <v>-0.8424585600000007</v>
       </c>
       <c r="O89">
-        <v>-0.1775283612000003</v>
+        <v>-0.1937654688000002</v>
       </c>
       <c r="P89">
-        <v>-0.5943340788000011</v>
+        <v>-0.6486930912000006</v>
       </c>
       <c r="Q89">
-        <v>-0.0343340788000015</v>
+        <v>-0.08869309120000102</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2873221929448765</v>
+        <v>0.3074490423569496</v>
       </c>
       <c r="T89">
-        <v>3.73627151159536</v>
+        <v>4.047627470894974</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2010953537409411</v>
+        <v>0.1988101792666123</v>
       </c>
       <c r="W89">
-        <v>0.1172792020708299</v>
+        <v>0.1176146656836613</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8743276249606136</v>
+        <v>0.8643920837678793</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1403947908844559</v>
+        <v>0.1414047908844559</v>
       </c>
       <c r="C90">
-        <v>-12.17273240099217</v>
+        <v>-12.8431088258487</v>
       </c>
       <c r="D90">
-        <v>26.39646759900783</v>
+        <v>26.2069911741513</v>
       </c>
       <c r="E90">
-        <v>40.8292</v>
+        <v>41.3101</v>
       </c>
       <c r="F90">
-        <v>42.3192</v>
+        <v>42.8001</v>
       </c>
       <c r="G90">
         <v>3.75</v>
@@ -8795,37 +8795,37 @@
         <v>5.37</v>
       </c>
       <c r="M90">
-        <v>6.212458560000001</v>
+        <v>6.28305468</v>
       </c>
       <c r="N90">
-        <v>-0.8424585600000007</v>
+        <v>-0.9130546800000001</v>
       </c>
       <c r="O90">
-        <v>-0.1937654688000002</v>
+        <v>-0.2100025764</v>
       </c>
       <c r="P90">
-        <v>-0.6486930912000006</v>
+        <v>-0.7030521036000001</v>
       </c>
       <c r="Q90">
-        <v>-0.08869309120000102</v>
+        <v>-0.1430521036000005</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3074490423569496</v>
+        <v>0.3312353189348541</v>
       </c>
       <c r="T90">
-        <v>4.047627470894974</v>
+        <v>4.415593604612699</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1988101792666123</v>
+        <v>0.1965763570276616</v>
       </c>
       <c r="W90">
-        <v>0.1176146656836613</v>
+        <v>0.1179425907883393</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8643920837678793</v>
+        <v>0.854679813163746</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1414047908844559</v>
+        <v>0.1424147908844559</v>
       </c>
       <c r="C91">
-        <v>-12.8431088258487</v>
+        <v>-13.51078447652591</v>
       </c>
       <c r="D91">
-        <v>26.2069911741513</v>
+        <v>26.0202155234741</v>
       </c>
       <c r="E91">
-        <v>41.3101</v>
+        <v>41.791</v>
       </c>
       <c r="F91">
-        <v>42.8001</v>
+        <v>43.28100000000001</v>
       </c>
       <c r="G91">
         <v>3.75</v>
@@ -8877,37 +8877,37 @@
         <v>5.37</v>
       </c>
       <c r="M91">
-        <v>6.28305468</v>
+        <v>6.353650800000001</v>
       </c>
       <c r="N91">
-        <v>-0.9130546800000001</v>
+        <v>-0.9836508000000013</v>
       </c>
       <c r="O91">
-        <v>-0.2100025764</v>
+        <v>-0.2262396840000003</v>
       </c>
       <c r="P91">
-        <v>-0.7030521036000001</v>
+        <v>-0.757411116000001</v>
       </c>
       <c r="Q91">
-        <v>-0.1430521036000005</v>
+        <v>-0.1974111160000014</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3312353189348541</v>
+        <v>0.3597788508283395</v>
       </c>
       <c r="T91">
-        <v>4.415593604612699</v>
+        <v>4.857152965073968</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1965763570276616</v>
+        <v>0.1943921752829098</v>
       </c>
       <c r="W91">
-        <v>0.1179425907883393</v>
+        <v>0.1182632286684689</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.854679813163746</v>
+        <v>0.8451833707952598</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1424147908844559</v>
+        <v>0.1434247908844559</v>
       </c>
       <c r="C92">
-        <v>-13.51078447652591</v>
+        <v>-14.17581668915825</v>
       </c>
       <c r="D92">
-        <v>26.0202155234741</v>
+        <v>25.83608331084175</v>
       </c>
       <c r="E92">
-        <v>41.791</v>
+        <v>42.2719</v>
       </c>
       <c r="F92">
-        <v>43.28100000000001</v>
+        <v>43.7619</v>
       </c>
       <c r="G92">
         <v>3.75</v>
@@ -8959,37 +8959,37 @@
         <v>5.37</v>
       </c>
       <c r="M92">
-        <v>6.353650800000001</v>
+        <v>6.424246920000002</v>
       </c>
       <c r="N92">
-        <v>-0.9836508000000013</v>
+        <v>-1.054246920000002</v>
       </c>
       <c r="O92">
-        <v>-0.2262396840000003</v>
+        <v>-0.2424767916000004</v>
       </c>
       <c r="P92">
-        <v>-0.757411116000001</v>
+        <v>-0.8117701284000012</v>
       </c>
       <c r="Q92">
-        <v>-0.1974111160000014</v>
+        <v>-0.2517701284000016</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3597788508283395</v>
+        <v>0.3946653898092662</v>
       </c>
       <c r="T92">
-        <v>4.857152965073968</v>
+        <v>5.396836627859966</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1943921752829098</v>
+        <v>0.1922559975325481</v>
       </c>
       <c r="W92">
-        <v>0.1182632286684689</v>
+        <v>0.1185768195622219</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8451833707952598</v>
+        <v>0.8358956414458613</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1434247908844559</v>
+        <v>0.1444347908844559</v>
       </c>
       <c r="C93">
-        <v>-14.17581668915825</v>
+        <v>-14.83826118832637</v>
       </c>
       <c r="D93">
-        <v>25.83608331084175</v>
+        <v>25.65453881167363</v>
       </c>
       <c r="E93">
-        <v>42.2719</v>
+        <v>42.7528</v>
       </c>
       <c r="F93">
-        <v>43.7619</v>
+        <v>44.2428</v>
       </c>
       <c r="G93">
         <v>3.75</v>
@@ -9041,37 +9041,37 @@
         <v>5.37</v>
       </c>
       <c r="M93">
-        <v>6.424246920000002</v>
+        <v>6.494843040000001</v>
       </c>
       <c r="N93">
-        <v>-1.054246920000002</v>
+        <v>-1.124843040000001</v>
       </c>
       <c r="O93">
-        <v>-0.2424767916000004</v>
+        <v>-0.2587138992000002</v>
       </c>
       <c r="P93">
-        <v>-0.8117701284000012</v>
+        <v>-0.8661291408000007</v>
       </c>
       <c r="Q93">
-        <v>-0.2517701284000016</v>
+        <v>-0.3061291408000011</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3946653898092662</v>
+        <v>0.4382735635354246</v>
       </c>
       <c r="T93">
-        <v>5.396836627859966</v>
+        <v>6.071441206342464</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1922559975325481</v>
+        <v>0.1901662584289335</v>
       </c>
       <c r="W93">
-        <v>0.1185768195622219</v>
+        <v>0.1188835932626326</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8358956414458613</v>
+        <v>0.8268098192562324</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1444347908844559</v>
+        <v>0.1454447908844559</v>
       </c>
       <c r="C94">
-        <v>-14.83826118832637</v>
+        <v>-15.49817214328219</v>
       </c>
       <c r="D94">
-        <v>25.65453881167363</v>
+        <v>25.47552785671782</v>
       </c>
       <c r="E94">
-        <v>42.7528</v>
+        <v>43.23370000000001</v>
       </c>
       <c r="F94">
-        <v>44.2428</v>
+        <v>44.72370000000001</v>
       </c>
       <c r="G94">
         <v>3.75</v>
@@ -9123,37 +9123,37 @@
         <v>5.37</v>
       </c>
       <c r="M94">
-        <v>6.494843040000001</v>
+        <v>6.565439160000002</v>
       </c>
       <c r="N94">
-        <v>-1.124843040000001</v>
+        <v>-1.195439160000002</v>
       </c>
       <c r="O94">
-        <v>-0.2587138992000002</v>
+        <v>-0.2749510068000005</v>
       </c>
       <c r="P94">
-        <v>-0.8661291408000007</v>
+        <v>-0.9204881532000015</v>
       </c>
       <c r="Q94">
-        <v>-0.3061291408000011</v>
+        <v>-0.3604881532000019</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4382735635354246</v>
+        <v>0.4943412154690567</v>
       </c>
       <c r="T94">
-        <v>6.071441206342464</v>
+        <v>6.938789950105674</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1901662584289335</v>
+        <v>0.188121459951203</v>
       </c>
       <c r="W94">
-        <v>0.1188835932626326</v>
+        <v>0.1191837696791634</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8268098192562324</v>
+        <v>0.8179193910921868</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1454447908844559</v>
+        <v>0.1464547908844559</v>
       </c>
       <c r="C95">
-        <v>-15.49817214328219</v>
+        <v>-16.15560222183628</v>
       </c>
       <c r="D95">
-        <v>25.47552785671782</v>
+        <v>25.29899777816373</v>
       </c>
       <c r="E95">
-        <v>43.23370000000001</v>
+        <v>43.7146</v>
       </c>
       <c r="F95">
-        <v>44.72370000000001</v>
+        <v>45.20460000000001</v>
       </c>
       <c r="G95">
         <v>3.75</v>
@@ -9205,37 +9205,37 @@
         <v>5.37</v>
       </c>
       <c r="M95">
-        <v>6.565439160000002</v>
+        <v>6.636035280000002</v>
       </c>
       <c r="N95">
-        <v>-1.195439160000002</v>
+        <v>-1.266035280000001</v>
       </c>
       <c r="O95">
-        <v>-0.2749510068000005</v>
+        <v>-0.2911881144000004</v>
       </c>
       <c r="P95">
-        <v>-0.9204881532000015</v>
+        <v>-0.9748471656000011</v>
       </c>
       <c r="Q95">
-        <v>-0.3604881532000019</v>
+        <v>-0.4148471656000015</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4943412154690567</v>
+        <v>0.5690980847138997</v>
       </c>
       <c r="T95">
-        <v>6.938789950105674</v>
+        <v>8.095254941789955</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.188121459951203</v>
+        <v>0.1861201678240625</v>
       </c>
       <c r="W95">
-        <v>0.1191837696791634</v>
+        <v>0.1194775593634276</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8179193910921868</v>
+        <v>0.8092181209741849</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1464547908844559</v>
+        <v>0.1474647908844559</v>
       </c>
       <c r="C96">
-        <v>-16.15560222183628</v>
+        <v>-16.81060264202043</v>
       </c>
       <c r="D96">
-        <v>25.29899777816373</v>
+        <v>25.12489735797958</v>
       </c>
       <c r="E96">
-        <v>43.7146</v>
+        <v>44.1955</v>
       </c>
       <c r="F96">
-        <v>45.20460000000001</v>
+        <v>45.6855</v>
       </c>
       <c r="G96">
         <v>3.75</v>
@@ -9287,37 +9287,37 @@
         <v>5.37</v>
       </c>
       <c r="M96">
-        <v>6.636035280000002</v>
+        <v>6.706631400000001</v>
       </c>
       <c r="N96">
-        <v>-1.266035280000001</v>
+        <v>-1.336631400000001</v>
       </c>
       <c r="O96">
-        <v>-0.2911881144000004</v>
+        <v>-0.3074252220000002</v>
       </c>
       <c r="P96">
-        <v>-0.9748471656000011</v>
+        <v>-1.029206178000001</v>
       </c>
       <c r="Q96">
-        <v>-0.4148471656000015</v>
+        <v>-0.469206178000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5690980847138997</v>
+        <v>0.6737577016566798</v>
       </c>
       <c r="T96">
-        <v>8.095254941789955</v>
+        <v>9.714305930147949</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1861201678240625</v>
+        <v>0.1841610081627566</v>
       </c>
       <c r="W96">
-        <v>0.1194775593634276</v>
+        <v>0.1197651640017073</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8092181209741849</v>
+        <v>0.8007000354902462</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1474647908844559</v>
+        <v>0.2021052855205376</v>
       </c>
       <c r="C97">
-        <v>-16.81060264202043</v>
+        <v>-24.1077583592058</v>
       </c>
       <c r="D97">
-        <v>25.12489735797958</v>
+        <v>18.30864164079421</v>
       </c>
       <c r="E97">
-        <v>44.1955</v>
+        <v>44.67640000000001</v>
       </c>
       <c r="F97">
-        <v>45.6855</v>
+        <v>46.16640000000001</v>
       </c>
       <c r="G97">
         <v>3.75</v>
@@ -9369,45 +9369,45 @@
         <v>5.37</v>
       </c>
       <c r="M97">
-        <v>6.706631400000001</v>
+        <v>9.270213120000003</v>
       </c>
       <c r="N97">
-        <v>-1.336631400000001</v>
+        <v>-3.900213120000003</v>
       </c>
       <c r="O97">
-        <v>-0.3074252220000002</v>
+        <v>-0.8970490176000007</v>
       </c>
       <c r="P97">
-        <v>-1.029206178000001</v>
+        <v>-3.003164102400002</v>
       </c>
       <c r="Q97">
-        <v>-0.469206178000001</v>
+        <v>-2.443164102400003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6737577016566798</v>
+        <v>0.8755094929728908</v>
       </c>
       <c r="T97">
-        <v>9.714305930147949</v>
+        <v>12.83534197705124</v>
       </c>
       <c r="U97">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1841610081627566</v>
+        <v>0.1332331828850122</v>
       </c>
       <c r="W97">
-        <v>0.1197651640017073</v>
+        <v>0.1740467768766896</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.8007000354902462</v>
+        <v>0.5792747081957053</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2021052855205376</v>
+        <v>0.2036552855205375</v>
       </c>
       <c r="C98">
-        <v>-24.10775835920579</v>
+        <v>-24.72848350898657</v>
       </c>
       <c r="D98">
-        <v>18.30864164079421</v>
+        <v>18.16881649101343</v>
       </c>
       <c r="E98">
-        <v>44.6764</v>
+        <v>45.1573</v>
       </c>
       <c r="F98">
-        <v>46.1664</v>
+        <v>46.6473</v>
       </c>
       <c r="G98">
         <v>3.75</v>
@@ -9451,37 +9451,37 @@
         <v>5.37</v>
       </c>
       <c r="M98">
-        <v>9.270213120000001</v>
+        <v>9.366777840000001</v>
       </c>
       <c r="N98">
-        <v>-3.900213120000001</v>
+        <v>-3.996777840000001</v>
       </c>
       <c r="O98">
-        <v>-0.8970490176000002</v>
+        <v>-0.9192589032000003</v>
       </c>
       <c r="P98">
-        <v>-3.003164102400001</v>
+        <v>-3.077518936800001</v>
       </c>
       <c r="Q98">
-        <v>-2.443164102400001</v>
+        <v>-2.517518936800001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8755094929728887</v>
+        <v>1.152079323963851</v>
       </c>
       <c r="T98">
-        <v>12.83534197705121</v>
+        <v>17.11378930273494</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1332331828850122</v>
+        <v>0.1318596449171255</v>
       </c>
       <c r="W98">
-        <v>0.1740467768766896</v>
+        <v>0.1743225833006412</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5792747081957054</v>
+        <v>0.5733028039875022</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2036552855205375</v>
+        <v>0.2052052855205375</v>
       </c>
       <c r="C99">
-        <v>-24.72848350898657</v>
+        <v>-25.34708912517867</v>
       </c>
       <c r="D99">
-        <v>18.16881649101343</v>
+        <v>18.03111087482133</v>
       </c>
       <c r="E99">
-        <v>45.1573</v>
+        <v>45.6382</v>
       </c>
       <c r="F99">
-        <v>46.6473</v>
+        <v>47.1282</v>
       </c>
       <c r="G99">
         <v>3.75</v>
@@ -9533,37 +9533,37 @@
         <v>5.37</v>
       </c>
       <c r="M99">
-        <v>9.366777840000001</v>
+        <v>9.463342560000001</v>
       </c>
       <c r="N99">
-        <v>-3.996777840000001</v>
+        <v>-4.093342560000001</v>
       </c>
       <c r="O99">
-        <v>-0.9192589032000003</v>
+        <v>-0.9414687888000003</v>
       </c>
       <c r="P99">
-        <v>-3.077518936800001</v>
+        <v>-3.1518737712</v>
       </c>
       <c r="Q99">
-        <v>-2.517518936800001</v>
+        <v>-2.591873771200001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.152079323963851</v>
+        <v>1.705218985945777</v>
       </c>
       <c r="T99">
-        <v>17.11378930273494</v>
+        <v>25.67068395410241</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1318596449171255</v>
+        <v>0.1305141383363385</v>
       </c>
       <c r="W99">
-        <v>0.1743225833006412</v>
+        <v>0.1745927610220632</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5733028039875022</v>
+        <v>0.5674527753753849</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2052052855205375</v>
+        <v>0.2067552855205375</v>
       </c>
       <c r="C100">
-        <v>-25.34708912517867</v>
+        <v>-25.96362303855145</v>
       </c>
       <c r="D100">
-        <v>18.03111087482133</v>
+        <v>17.89547696144856</v>
       </c>
       <c r="E100">
-        <v>45.6382</v>
+        <v>46.1191</v>
       </c>
       <c r="F100">
-        <v>47.1282</v>
+        <v>47.60910000000001</v>
       </c>
       <c r="G100">
         <v>3.75</v>
@@ -9615,37 +9615,37 @@
         <v>5.37</v>
       </c>
       <c r="M100">
-        <v>9.463342560000001</v>
+        <v>9.559907280000001</v>
       </c>
       <c r="N100">
-        <v>-4.093342560000001</v>
+        <v>-4.189907280000001</v>
       </c>
       <c r="O100">
-        <v>-0.9414687888000003</v>
+        <v>-0.9636786744000002</v>
       </c>
       <c r="P100">
-        <v>-3.1518737712</v>
+        <v>-3.226228605600001</v>
       </c>
       <c r="Q100">
-        <v>-2.591873771200001</v>
+        <v>-2.666228605600001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.705218985945777</v>
+        <v>3.364637971891554</v>
       </c>
       <c r="T100">
-        <v>25.67068395410241</v>
+        <v>51.34136790820482</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1305141383363385</v>
+        <v>0.1291958137066785</v>
       </c>
       <c r="W100">
-        <v>0.1745927610220632</v>
+        <v>0.174857480607699</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5674527753753849</v>
+        <v>0.5617209291594719</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2067552855205375</v>
-      </c>
-      <c r="C101">
-        <v>-25.96362303855145</v>
-      </c>
-      <c r="D101">
-        <v>17.89547696144856</v>
-      </c>
-      <c r="E101">
-        <v>46.1191</v>
-      </c>
-      <c r="F101">
-        <v>47.60910000000001</v>
-      </c>
-      <c r="G101">
-        <v>3.75</v>
-      </c>
-      <c r="H101">
-        <v>46.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.93</v>
-      </c>
-      <c r="K101">
-        <v>0.5599999999999996</v>
-      </c>
-      <c r="L101">
-        <v>5.37</v>
-      </c>
-      <c r="M101">
-        <v>9.559907280000001</v>
-      </c>
-      <c r="N101">
-        <v>-4.189907280000001</v>
-      </c>
-      <c r="O101">
-        <v>-0.9636786744000002</v>
-      </c>
-      <c r="P101">
-        <v>-3.226228605600001</v>
-      </c>
-      <c r="Q101">
-        <v>-2.666228605600001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.364637971891554</v>
-      </c>
-      <c r="T101">
-        <v>51.34136790820482</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1291958137066785</v>
-      </c>
-      <c r="W101">
-        <v>0.174857480607699</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5617209291594719</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
